--- a/Thesis/data/raw/autoic/coded-TedK_Longitudinal.xlsx
+++ b/Thesis/data/raw/autoic/coded-TedK_Longitudinal.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kathrene.conway\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b4dcdb2932ef22e/Documents/Integrative-Data-Project/Thesis/data/raw/autoic/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_22A9EB38F104CCB08B30471301005BB83B519864" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE7E005-D7BB-4A31-9B2B-39CC95F0733C}"/>
   <bookViews>
-    <workbookView xWindow="190" yWindow="0" windowWidth="19030" windowHeight="8700" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paragraph" sheetId="1" r:id="rId1"/>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="585">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="588">
   <si>
     <t>Document</t>
   </si>
@@ -1778,12 +1779,21 @@
   </si>
   <si>
     <t xml:space="preserve"> good of society each baby when it is born will have its mind adjusted by scientists so that it will grow up to be a healthy happy public spirited citizen anxious to be useful to the community and if anybody doesn't like all this the psychologists of the future will be able to fix him so he does like it .</t>
+  </si>
+  <si>
+    <t>A Fantasy_1999.txt</t>
+  </si>
+  <si>
+    <t>Morality and Revolution First Edition_1999.txt</t>
+  </si>
+  <si>
+    <t>Morality and Revolution Third Edition_2001.txt</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1828,11 +1838,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1854,9 +1864,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1894,9 +1904,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1931,7 +1941,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1966,7 +1976,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2139,20 +2149,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:N539"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.90625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="56.36328125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="6.453125" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="56.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.42578125" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="2" customFormat="1" ht="39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" s="2" customFormat="1" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2196,7 +2206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -2240,7 +2250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -2284,7 +2294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
@@ -2328,7 +2338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>31</v>
       </c>
@@ -2372,7 +2382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>31</v>
       </c>
@@ -2416,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -2460,7 +2470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -2504,7 +2514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>31</v>
       </c>
@@ -2548,7 +2558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>31</v>
       </c>
@@ -2592,7 +2602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>31</v>
       </c>
@@ -2636,7 +2646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>31</v>
       </c>
@@ -2680,7 +2690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>31</v>
       </c>
@@ -2724,7 +2734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>31</v>
       </c>
@@ -2768,7 +2778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
@@ -2812,7 +2822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -2856,7 +2866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>31</v>
       </c>
@@ -2900,7 +2910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>32</v>
       </c>
@@ -2944,7 +2954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>32</v>
       </c>
@@ -2988,7 +2998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>32</v>
       </c>
@@ -3032,7 +3042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>32</v>
       </c>
@@ -3076,7 +3086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>32</v>
       </c>
@@ -3120,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>32</v>
       </c>
@@ -3164,7 +3174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -3208,7 +3218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
@@ -3252,7 +3262,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
@@ -3296,7 +3306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>32</v>
       </c>
@@ -3340,7 +3350,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>32</v>
       </c>
@@ -3384,7 +3394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="125" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>32</v>
       </c>
@@ -3428,7 +3438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>33</v>
       </c>
@@ -3472,7 +3482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>33</v>
       </c>
@@ -3516,7 +3526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>33</v>
       </c>
@@ -3560,7 +3570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>33</v>
       </c>
@@ -3604,7 +3614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -3648,7 +3658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -3692,7 +3702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>33</v>
       </c>
@@ -3736,7 +3746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>33</v>
       </c>
@@ -3780,7 +3790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>33</v>
       </c>
@@ -3824,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>34</v>
       </c>
@@ -3868,7 +3878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>34</v>
       </c>
@@ -3912,7 +3922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3956,7 +3966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>34</v>
       </c>
@@ -4000,7 +4010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>35</v>
       </c>
@@ -4044,7 +4054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>35</v>
       </c>
@@ -4088,7 +4098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
@@ -4132,7 +4142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>35</v>
       </c>
@@ -4176,7 +4186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>35</v>
       </c>
@@ -4220,7 +4230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>35</v>
       </c>
@@ -4264,7 +4274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>35</v>
       </c>
@@ -4308,7 +4318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>35</v>
       </c>
@@ -4352,7 +4362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>35</v>
       </c>
@@ -4396,7 +4406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>36</v>
       </c>
@@ -4440,7 +4450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>36</v>
       </c>
@@ -4484,7 +4494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>36</v>
       </c>
@@ -4528,7 +4538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>36</v>
       </c>
@@ -4572,7 +4582,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="56" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>36</v>
       </c>
@@ -4616,7 +4626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>36</v>
       </c>
@@ -4660,7 +4670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>36</v>
       </c>
@@ -4704,7 +4714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>36</v>
       </c>
@@ -4748,7 +4758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>36</v>
       </c>
@@ -4792,7 +4802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>36</v>
       </c>
@@ -4836,7 +4846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>36</v>
       </c>
@@ -4880,7 +4890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>36</v>
       </c>
@@ -4924,7 +4934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>36</v>
       </c>
@@ -4968,7 +4978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>36</v>
       </c>
@@ -5012,7 +5022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>36</v>
       </c>
@@ -5056,7 +5066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>36</v>
       </c>
@@ -5100,7 +5110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -5144,7 +5154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>36</v>
       </c>
@@ -5188,7 +5198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>36</v>
       </c>
@@ -5232,7 +5242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>36</v>
       </c>
@@ -5276,7 +5286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>36</v>
       </c>
@@ -5320,7 +5330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>36</v>
       </c>
@@ -5364,7 +5374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>36</v>
       </c>
@@ -5408,7 +5418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>36</v>
       </c>
@@ -5452,7 +5462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>36</v>
       </c>
@@ -5496,7 +5506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>36</v>
       </c>
@@ -5540,7 +5550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>36</v>
       </c>
@@ -5584,7 +5594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>36</v>
       </c>
@@ -5628,7 +5638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>36</v>
       </c>
@@ -5672,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>36</v>
       </c>
@@ -5716,7 +5726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>36</v>
       </c>
@@ -5760,7 +5770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>36</v>
       </c>
@@ -5804,7 +5814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>36</v>
       </c>
@@ -5848,7 +5858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>36</v>
       </c>
@@ -5892,7 +5902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>36</v>
       </c>
@@ -5936,7 +5946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>36</v>
       </c>
@@ -5980,7 +5990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>36</v>
       </c>
@@ -6024,7 +6034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>36</v>
       </c>
@@ -6068,7 +6078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>36</v>
       </c>
@@ -6112,7 +6122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>36</v>
       </c>
@@ -6156,7 +6166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>36</v>
       </c>
@@ -6200,7 +6210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
         <v>36</v>
       </c>
@@ -6244,7 +6254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>36</v>
       </c>
@@ -6288,7 +6298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>36</v>
       </c>
@@ -6332,7 +6342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>36</v>
       </c>
@@ -6376,7 +6386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>36</v>
       </c>
@@ -6420,7 +6430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>36</v>
       </c>
@@ -6464,7 +6474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>36</v>
       </c>
@@ -6508,7 +6518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>36</v>
       </c>
@@ -6552,7 +6562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="25" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>36</v>
       </c>
@@ -6596,7 +6606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
         <v>37</v>
       </c>
@@ -6640,7 +6650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>37</v>
       </c>
@@ -6684,7 +6694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>37</v>
       </c>
@@ -6728,7 +6738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>37</v>
       </c>
@@ -6772,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>37</v>
       </c>
@@ -6816,7 +6826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>37</v>
       </c>
@@ -6860,7 +6870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>37</v>
       </c>
@@ -6904,7 +6914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>37</v>
       </c>
@@ -6948,7 +6958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>37</v>
       </c>
@@ -6992,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>37</v>
       </c>
@@ -7036,7 +7046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>37</v>
       </c>
@@ -7080,7 +7090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>37</v>
       </c>
@@ -7124,7 +7134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>37</v>
       </c>
@@ -7168,7 +7178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>37</v>
       </c>
@@ -7212,7 +7222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
         <v>37</v>
       </c>
@@ -7256,7 +7266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>37</v>
       </c>
@@ -7300,7 +7310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>37</v>
       </c>
@@ -7344,7 +7354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>37</v>
       </c>
@@ -7388,7 +7398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>37</v>
       </c>
@@ -7432,7 +7442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>37</v>
       </c>
@@ -7476,7 +7486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>37</v>
       </c>
@@ -7520,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>37</v>
       </c>
@@ -7564,7 +7574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>37</v>
       </c>
@@ -7608,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>37</v>
       </c>
@@ -7652,7 +7662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>37</v>
       </c>
@@ -7696,7 +7706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>37</v>
       </c>
@@ -7740,7 +7750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>37</v>
       </c>
@@ -7784,7 +7794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>37</v>
       </c>
@@ -7828,7 +7838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>37</v>
       </c>
@@ -7872,7 +7882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>37</v>
       </c>
@@ -7916,7 +7926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>37</v>
       </c>
@@ -7960,7 +7970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>37</v>
       </c>
@@ -8004,7 +8014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
         <v>37</v>
       </c>
@@ -8048,7 +8058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>37</v>
       </c>
@@ -8092,7 +8102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
         <v>37</v>
       </c>
@@ -8136,7 +8146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>37</v>
       </c>
@@ -8180,7 +8190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
         <v>37</v>
       </c>
@@ -8224,7 +8234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
         <v>37</v>
       </c>
@@ -8268,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
         <v>37</v>
       </c>
@@ -8312,7 +8322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
         <v>37</v>
       </c>
@@ -8356,7 +8366,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="142" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
         <v>37</v>
       </c>
@@ -8400,7 +8410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
         <v>37</v>
       </c>
@@ -8444,7 +8454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
         <v>37</v>
       </c>
@@ -8488,7 +8498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
         <v>37</v>
       </c>
@@ -8532,7 +8542,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="146" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
         <v>37</v>
       </c>
@@ -8576,7 +8586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
         <v>37</v>
       </c>
@@ -8620,7 +8630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
         <v>37</v>
       </c>
@@ -8664,7 +8674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
         <v>37</v>
       </c>
@@ -8708,7 +8718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
         <v>37</v>
       </c>
@@ -8752,7 +8762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
         <v>37</v>
       </c>
@@ -8796,7 +8806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
         <v>37</v>
       </c>
@@ -8840,7 +8850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
         <v>37</v>
       </c>
@@ -8884,7 +8894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
         <v>37</v>
       </c>
@@ -8928,7 +8938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
         <v>37</v>
       </c>
@@ -8972,7 +8982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
         <v>37</v>
       </c>
@@ -9016,7 +9026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
         <v>37</v>
       </c>
@@ -9060,7 +9070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
         <v>37</v>
       </c>
@@ -9104,7 +9114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
         <v>37</v>
       </c>
@@ -9148,7 +9158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
         <v>37</v>
       </c>
@@ -9192,7 +9202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>37</v>
       </c>
@@ -9236,7 +9246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
         <v>37</v>
       </c>
@@ -9280,7 +9290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
         <v>37</v>
       </c>
@@ -9324,7 +9334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
         <v>38</v>
       </c>
@@ -9368,7 +9378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
         <v>38</v>
       </c>
@@ -9412,7 +9422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
         <v>38</v>
       </c>
@@ -9456,7 +9466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>38</v>
       </c>
@@ -9500,7 +9510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
         <v>38</v>
       </c>
@@ -9544,7 +9554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
         <v>38</v>
       </c>
@@ -9588,7 +9598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
         <v>38</v>
       </c>
@@ -9632,7 +9642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
         <v>38</v>
       </c>
@@ -9676,7 +9686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
         <v>38</v>
       </c>
@@ -9720,7 +9730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>38</v>
       </c>
@@ -9764,7 +9774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
         <v>38</v>
       </c>
@@ -9808,7 +9818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
         <v>38</v>
       </c>
@@ -9852,7 +9862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
         <v>38</v>
       </c>
@@ -9896,7 +9906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
         <v>38</v>
       </c>
@@ -9940,7 +9950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
         <v>38</v>
       </c>
@@ -9984,7 +9994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
         <v>38</v>
       </c>
@@ -10028,7 +10038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
         <v>38</v>
       </c>
@@ -10072,7 +10082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
         <v>38</v>
       </c>
@@ -10116,7 +10126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
         <v>38</v>
       </c>
@@ -10160,7 +10170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
         <v>38</v>
       </c>
@@ -10204,7 +10214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
         <v>38</v>
       </c>
@@ -10248,7 +10258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
         <v>38</v>
       </c>
@@ -10292,7 +10302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
         <v>38</v>
       </c>
@@ -10336,7 +10346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
         <v>38</v>
       </c>
@@ -10380,7 +10390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>38</v>
       </c>
@@ -10424,7 +10434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
         <v>38</v>
       </c>
@@ -10468,7 +10478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
         <v>38</v>
       </c>
@@ -10512,7 +10522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
         <v>38</v>
       </c>
@@ -10556,7 +10566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
         <v>38</v>
       </c>
@@ -10600,7 +10610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
         <v>38</v>
       </c>
@@ -10644,7 +10654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>38</v>
       </c>
@@ -10688,7 +10698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
         <v>38</v>
       </c>
@@ -10732,7 +10742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
         <v>38</v>
       </c>
@@ -10776,7 +10786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
         <v>38</v>
       </c>
@@ -10820,7 +10830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
         <v>38</v>
       </c>
@@ -10864,7 +10874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
         <v>38</v>
       </c>
@@ -10908,7 +10918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
         <v>38</v>
       </c>
@@ -10952,7 +10962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>38</v>
       </c>
@@ -10996,7 +11006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
         <v>38</v>
       </c>
@@ -11040,7 +11050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
         <v>38</v>
       </c>
@@ -11084,7 +11094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
         <v>38</v>
       </c>
@@ -11128,7 +11138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
         <v>38</v>
       </c>
@@ -11172,7 +11182,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="206" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
         <v>38</v>
       </c>
@@ -11216,7 +11226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>38</v>
       </c>
@@ -11260,7 +11270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
         <v>38</v>
       </c>
@@ -11304,7 +11314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
         <v>38</v>
       </c>
@@ -11348,7 +11358,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="210" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
         <v>38</v>
       </c>
@@ -11392,7 +11402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
         <v>38</v>
       </c>
@@ -11436,7 +11446,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="212" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
         <v>38</v>
       </c>
@@ -11480,7 +11490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
         <v>38</v>
       </c>
@@ -11524,7 +11534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>38</v>
       </c>
@@ -11568,7 +11578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
         <v>38</v>
       </c>
@@ -11612,7 +11622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
         <v>38</v>
       </c>
@@ -11656,7 +11666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
         <v>38</v>
       </c>
@@ -11700,7 +11710,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="218" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
         <v>38</v>
       </c>
@@ -11744,7 +11754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
         <v>38</v>
       </c>
@@ -11788,7 +11798,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="220" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>38</v>
       </c>
@@ -11832,7 +11842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
         <v>38</v>
       </c>
@@ -11876,7 +11886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
         <v>38</v>
       </c>
@@ -11920,7 +11930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
         <v>38</v>
       </c>
@@ -11964,7 +11974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
         <v>38</v>
       </c>
@@ -12008,7 +12018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
         <v>39</v>
       </c>
@@ -12052,7 +12062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
         <v>39</v>
       </c>
@@ -12096,7 +12106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
         <v>39</v>
       </c>
@@ -12140,7 +12150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
         <v>39</v>
       </c>
@@ -12184,7 +12194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>39</v>
       </c>
@@ -12228,7 +12238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
         <v>39</v>
       </c>
@@ -12272,7 +12282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
         <v>39</v>
       </c>
@@ -12316,7 +12326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
         <v>39</v>
       </c>
@@ -12360,7 +12370,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="233" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
         <v>39</v>
       </c>
@@ -12404,7 +12414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
         <v>39</v>
       </c>
@@ -12448,7 +12458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>39</v>
       </c>
@@ -12492,7 +12502,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="236" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
         <v>39</v>
       </c>
@@ -12536,7 +12546,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="237" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
         <v>39</v>
       </c>
@@ -12580,7 +12590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
         <v>39</v>
       </c>
@@ -12624,7 +12634,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="239" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
         <v>39</v>
       </c>
@@ -12668,7 +12678,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="240" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
         <v>39</v>
       </c>
@@ -12712,7 +12722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
         <v>39</v>
       </c>
@@ -12756,7 +12766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
         <v>39</v>
       </c>
@@ -12800,7 +12810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
         <v>39</v>
       </c>
@@ -12844,7 +12854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>39</v>
       </c>
@@ -12888,7 +12898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
         <v>39</v>
       </c>
@@ -12932,7 +12942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
         <v>39</v>
       </c>
@@ -12976,7 +12986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
         <v>39</v>
       </c>
@@ -13020,7 +13030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
         <v>39</v>
       </c>
@@ -13064,7 +13074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
         <v>39</v>
       </c>
@@ -13108,7 +13118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>39</v>
       </c>
@@ -13152,7 +13162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
         <v>39</v>
       </c>
@@ -13196,7 +13206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
         <v>39</v>
       </c>
@@ -13240,7 +13250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
         <v>39</v>
       </c>
@@ -13284,7 +13294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
         <v>39</v>
       </c>
@@ -13328,7 +13338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
         <v>39</v>
       </c>
@@ -13372,7 +13382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
         <v>39</v>
       </c>
@@ -13416,7 +13426,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="257" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
         <v>39</v>
       </c>
@@ -13460,7 +13470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
         <v>39</v>
       </c>
@@ -13504,7 +13514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
         <v>39</v>
       </c>
@@ -13548,7 +13558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>39</v>
       </c>
@@ -13592,7 +13602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
         <v>39</v>
       </c>
@@ -13636,7 +13646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
         <v>39</v>
       </c>
@@ -13680,7 +13690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
         <v>39</v>
       </c>
@@ -13724,7 +13734,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="264" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
         <v>39</v>
       </c>
@@ -13768,7 +13778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
         <v>39</v>
       </c>
@@ -13812,7 +13822,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="266" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
         <v>39</v>
       </c>
@@ -13856,7 +13866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
         <v>39</v>
       </c>
@@ -13900,7 +13910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
         <v>39</v>
       </c>
@@ -13944,7 +13954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
         <v>39</v>
       </c>
@@ -13988,7 +13998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
         <v>39</v>
       </c>
@@ -14032,7 +14042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
         <v>39</v>
       </c>
@@ -14076,7 +14086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
         <v>39</v>
       </c>
@@ -14120,7 +14130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
         <v>39</v>
       </c>
@@ -14164,7 +14174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
         <v>39</v>
       </c>
@@ -14208,7 +14218,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
         <v>39</v>
       </c>
@@ -14252,7 +14262,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="276" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
         <v>39</v>
       </c>
@@ -14296,7 +14306,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="277" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
         <v>39</v>
       </c>
@@ -14340,7 +14350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
         <v>39</v>
       </c>
@@ -14384,7 +14394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
         <v>39</v>
       </c>
@@ -14428,7 +14438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
         <v>39</v>
       </c>
@@ -14472,7 +14482,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="281" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
         <v>39</v>
       </c>
@@ -14516,7 +14526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
         <v>39</v>
       </c>
@@ -14560,7 +14570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
         <v>39</v>
       </c>
@@ -14604,7 +14614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
         <v>39</v>
       </c>
@@ -14648,7 +14658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
         <v>39</v>
       </c>
@@ -14692,7 +14702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
         <v>39</v>
       </c>
@@ -14736,7 +14746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
         <v>39</v>
       </c>
@@ -14780,7 +14790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
         <v>39</v>
       </c>
@@ -14824,7 +14834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
         <v>39</v>
       </c>
@@ -14868,7 +14878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
         <v>39</v>
       </c>
@@ -14912,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
         <v>39</v>
       </c>
@@ -14956,7 +14966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
         <v>39</v>
       </c>
@@ -15000,7 +15010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
         <v>39</v>
       </c>
@@ -15044,7 +15054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
         <v>39</v>
       </c>
@@ -15088,7 +15098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>39</v>
       </c>
@@ -15132,7 +15142,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="296" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
         <v>39</v>
       </c>
@@ -15176,7 +15186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
         <v>39</v>
       </c>
@@ -15220,7 +15230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
         <v>39</v>
       </c>
@@ -15264,7 +15274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
         <v>39</v>
       </c>
@@ -15308,7 +15318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
         <v>39</v>
       </c>
@@ -15352,7 +15362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
         <v>39</v>
       </c>
@@ -15396,7 +15406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
         <v>39</v>
       </c>
@@ -15440,7 +15450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
         <v>39</v>
       </c>
@@ -15484,7 +15494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
         <v>39</v>
       </c>
@@ -15528,7 +15538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
         <v>39</v>
       </c>
@@ -15572,7 +15582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
         <v>39</v>
       </c>
@@ -15616,7 +15626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
         <v>39</v>
       </c>
@@ -15660,7 +15670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
         <v>39</v>
       </c>
@@ -15704,7 +15714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
         <v>40</v>
       </c>
@@ -15748,7 +15758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
         <v>40</v>
       </c>
@@ -15792,7 +15802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
         <v>40</v>
       </c>
@@ -15836,7 +15846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
         <v>40</v>
       </c>
@@ -15880,7 +15890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
         <v>40</v>
       </c>
@@ -15924,7 +15934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
         <v>40</v>
       </c>
@@ -15968,7 +15978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
         <v>40</v>
       </c>
@@ -16012,7 +16022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
         <v>40</v>
       </c>
@@ -16056,7 +16066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
         <v>40</v>
       </c>
@@ -16100,7 +16110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
         <v>40</v>
       </c>
@@ -16144,7 +16154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
         <v>40</v>
       </c>
@@ -16188,7 +16198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
         <v>40</v>
       </c>
@@ -16232,7 +16242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
         <v>40</v>
       </c>
@@ -16276,7 +16286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
         <v>40</v>
       </c>
@@ -16320,7 +16330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
         <v>40</v>
       </c>
@@ -16364,7 +16374,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="324" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
         <v>40</v>
       </c>
@@ -16408,7 +16418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
         <v>40</v>
       </c>
@@ -16452,7 +16462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
         <v>40</v>
       </c>
@@ -16496,7 +16506,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="327" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
         <v>40</v>
       </c>
@@ -16540,7 +16550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
         <v>40</v>
       </c>
@@ -16584,7 +16594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
         <v>40</v>
       </c>
@@ -16628,7 +16638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
         <v>41</v>
       </c>
@@ -16672,7 +16682,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="331" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
         <v>41</v>
       </c>
@@ -16716,7 +16726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
         <v>41</v>
       </c>
@@ -16760,7 +16770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
         <v>41</v>
       </c>
@@ -16804,7 +16814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
         <v>41</v>
       </c>
@@ -16848,7 +16858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
         <v>41</v>
       </c>
@@ -16892,7 +16902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
         <v>41</v>
       </c>
@@ -16936,7 +16946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
         <v>41</v>
       </c>
@@ -16980,7 +16990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
         <v>41</v>
       </c>
@@ -17024,7 +17034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
         <v>41</v>
       </c>
@@ -17068,7 +17078,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="340" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
         <v>41</v>
       </c>
@@ -17112,7 +17122,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="341" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
         <v>41</v>
       </c>
@@ -17156,7 +17166,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
         <v>41</v>
       </c>
@@ -17200,7 +17210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
         <v>41</v>
       </c>
@@ -17244,7 +17254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
         <v>41</v>
       </c>
@@ -17288,7 +17298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
         <v>41</v>
       </c>
@@ -17332,7 +17342,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="346" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
         <v>41</v>
       </c>
@@ -17376,7 +17386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
         <v>41</v>
       </c>
@@ -17420,7 +17430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
         <v>41</v>
       </c>
@@ -17464,7 +17474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
         <v>41</v>
       </c>
@@ -17508,7 +17518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
         <v>41</v>
       </c>
@@ -17552,7 +17562,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="351" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
         <v>41</v>
       </c>
@@ -17596,7 +17606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
         <v>41</v>
       </c>
@@ -17640,7 +17650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="353" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
         <v>41</v>
       </c>
@@ -17684,7 +17694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
         <v>41</v>
       </c>
@@ -17728,7 +17738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
         <v>41</v>
       </c>
@@ -17772,7 +17782,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="356" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
         <v>41</v>
       </c>
@@ -17816,7 +17826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
         <v>41</v>
       </c>
@@ -17860,7 +17870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
         <v>41</v>
       </c>
@@ -17904,7 +17914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
         <v>41</v>
       </c>
@@ -17948,7 +17958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
         <v>41</v>
       </c>
@@ -17992,7 +18002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
         <v>41</v>
       </c>
@@ -18036,7 +18046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
         <v>41</v>
       </c>
@@ -18080,7 +18090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
         <v>41</v>
       </c>
@@ -18124,7 +18134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
         <v>41</v>
       </c>
@@ -18168,7 +18178,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="365" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
         <v>41</v>
       </c>
@@ -18212,7 +18222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
         <v>41</v>
       </c>
@@ -18256,7 +18266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
         <v>41</v>
       </c>
@@ -18300,7 +18310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
         <v>41</v>
       </c>
@@ -18344,7 +18354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
         <v>41</v>
       </c>
@@ -18388,7 +18398,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
         <v>41</v>
       </c>
@@ -18432,7 +18442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
         <v>41</v>
       </c>
@@ -18476,7 +18486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
         <v>41</v>
       </c>
@@ -18520,7 +18530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="373" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
         <v>41</v>
       </c>
@@ -18564,7 +18574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="374" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
         <v>41</v>
       </c>
@@ -18608,7 +18618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="375" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
         <v>41</v>
       </c>
@@ -18652,7 +18662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="376" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
         <v>41</v>
       </c>
@@ -18696,7 +18706,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="377" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
         <v>41</v>
       </c>
@@ -18740,7 +18750,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="378" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
         <v>41</v>
       </c>
@@ -18784,7 +18794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
         <v>41</v>
       </c>
@@ -18828,7 +18838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
         <v>41</v>
       </c>
@@ -18872,7 +18882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="381" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
         <v>41</v>
       </c>
@@ -18916,7 +18926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
         <v>41</v>
       </c>
@@ -18960,7 +18970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
         <v>41</v>
       </c>
@@ -19004,7 +19014,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="384" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
         <v>41</v>
       </c>
@@ -19048,7 +19058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="385" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
         <v>41</v>
       </c>
@@ -19092,7 +19102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
         <v>41</v>
       </c>
@@ -19136,7 +19146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
         <v>41</v>
       </c>
@@ -19180,7 +19190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
         <v>41</v>
       </c>
@@ -19224,7 +19234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="389" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
         <v>41</v>
       </c>
@@ -19268,7 +19278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="390" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
         <v>41</v>
       </c>
@@ -19312,7 +19322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="391" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
         <v>41</v>
       </c>
@@ -19356,7 +19366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
         <v>41</v>
       </c>
@@ -19400,7 +19410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="393" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
         <v>41</v>
       </c>
@@ -19444,7 +19454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="394" spans="1:14" ht="37.5" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
         <v>41</v>
       </c>
@@ -19488,7 +19498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
         <v>42</v>
       </c>
@@ -19532,7 +19542,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="396" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
         <v>42</v>
       </c>
@@ -19576,7 +19586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
         <v>42</v>
       </c>
@@ -19620,7 +19630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
         <v>42</v>
       </c>
@@ -19664,7 +19674,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="399" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
         <v>42</v>
       </c>
@@ -19708,7 +19718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
         <v>42</v>
       </c>
@@ -19752,7 +19762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="401" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
         <v>42</v>
       </c>
@@ -19796,7 +19806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="402" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
         <v>42</v>
       </c>
@@ -19840,7 +19850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="403" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
         <v>42</v>
       </c>
@@ -19884,7 +19894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="404" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
         <v>42</v>
       </c>
@@ -19928,7 +19938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="405" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
         <v>42</v>
       </c>
@@ -19972,7 +19982,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="406" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
         <v>42</v>
       </c>
@@ -20016,7 +20026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="407" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
         <v>42</v>
       </c>
@@ -20060,7 +20070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="408" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
         <v>42</v>
       </c>
@@ -20104,7 +20114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="409" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
         <v>42</v>
       </c>
@@ -20148,7 +20158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="410" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
         <v>42</v>
       </c>
@@ -20192,7 +20202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="411" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
         <v>42</v>
       </c>
@@ -20236,7 +20246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="412" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
         <v>42</v>
       </c>
@@ -20280,7 +20290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="413" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
         <v>42</v>
       </c>
@@ -20324,7 +20334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="414" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
         <v>42</v>
       </c>
@@ -20368,7 +20378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
         <v>42</v>
       </c>
@@ -20412,7 +20422,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="416" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
         <v>42</v>
       </c>
@@ -20456,7 +20466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
         <v>42</v>
       </c>
@@ -20500,7 +20510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
         <v>42</v>
       </c>
@@ -20544,7 +20554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="419" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
         <v>42</v>
       </c>
@@ -20588,7 +20598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="420" spans="1:14" ht="112.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
         <v>42</v>
       </c>
@@ -20632,7 +20642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
         <v>42</v>
       </c>
@@ -20676,7 +20686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="422" spans="1:14" ht="50" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
         <v>42</v>
       </c>
@@ -20720,7 +20730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="423" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
         <v>43</v>
       </c>
@@ -20764,7 +20774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
         <v>43</v>
       </c>
@@ -20808,7 +20818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
         <v>43</v>
       </c>
@@ -20852,7 +20862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
         <v>43</v>
       </c>
@@ -20896,7 +20906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
         <v>43</v>
       </c>
@@ -20940,7 +20950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
         <v>43</v>
       </c>
@@ -20984,7 +20994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="429" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
         <v>43</v>
       </c>
@@ -21028,7 +21038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
         <v>43</v>
       </c>
@@ -21072,7 +21082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="431" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
         <v>43</v>
       </c>
@@ -21116,7 +21126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="432" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
         <v>43</v>
       </c>
@@ -21160,7 +21170,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="433" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
         <v>43</v>
       </c>
@@ -21204,7 +21214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
         <v>43</v>
       </c>
@@ -21248,7 +21258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="435" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
         <v>43</v>
       </c>
@@ -21292,7 +21302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
         <v>43</v>
       </c>
@@ -21336,7 +21346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="437" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
         <v>43</v>
       </c>
@@ -21380,7 +21390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="438" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
         <v>43</v>
       </c>
@@ -21424,7 +21434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="439" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
         <v>43</v>
       </c>
@@ -21468,7 +21478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="440" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
         <v>43</v>
       </c>
@@ -21512,7 +21522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="441" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
         <v>43</v>
       </c>
@@ -21556,7 +21566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
         <v>43</v>
       </c>
@@ -21600,7 +21610,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="443" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
         <v>43</v>
       </c>
@@ -21644,7 +21654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
         <v>43</v>
       </c>
@@ -21688,7 +21698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
         <v>43</v>
       </c>
@@ -21732,7 +21742,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="446" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
         <v>43</v>
       </c>
@@ -21776,7 +21786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="447" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
         <v>43</v>
       </c>
@@ -21820,7 +21830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="448" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
         <v>44</v>
       </c>
@@ -21864,7 +21874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
         <v>44</v>
       </c>
@@ -21908,7 +21918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
         <v>44</v>
       </c>
@@ -21952,7 +21962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
         <v>44</v>
       </c>
@@ -21996,7 +22006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
         <v>44</v>
       </c>
@@ -22040,7 +22050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
         <v>44</v>
       </c>
@@ -22084,7 +22094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
         <v>44</v>
       </c>
@@ -22128,7 +22138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
         <v>44</v>
       </c>
@@ -22172,7 +22182,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="456" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
         <v>44</v>
       </c>
@@ -22216,7 +22226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
         <v>44</v>
       </c>
@@ -22260,7 +22270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
         <v>44</v>
       </c>
@@ -22304,7 +22314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
         <v>44</v>
       </c>
@@ -22348,7 +22358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
         <v>44</v>
       </c>
@@ -22392,7 +22402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
         <v>44</v>
       </c>
@@ -22436,7 +22446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
         <v>44</v>
       </c>
@@ -22480,7 +22490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
         <v>44</v>
       </c>
@@ -22524,7 +22534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
         <v>44</v>
       </c>
@@ -22568,7 +22578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="465" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
         <v>44</v>
       </c>
@@ -22612,7 +22622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
         <v>44</v>
       </c>
@@ -22656,7 +22666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="467" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
         <v>44</v>
       </c>
@@ -22700,7 +22710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
         <v>44</v>
       </c>
@@ -22744,7 +22754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="469" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
         <v>44</v>
       </c>
@@ -22788,7 +22798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="470" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
         <v>44</v>
       </c>
@@ -22832,7 +22842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
         <v>45</v>
       </c>
@@ -22876,7 +22886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
         <v>45</v>
       </c>
@@ -22920,7 +22930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
         <v>45</v>
       </c>
@@ -22964,7 +22974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
         <v>45</v>
       </c>
@@ -23008,7 +23018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="475" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
         <v>45</v>
       </c>
@@ -23052,7 +23062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="476" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
         <v>45</v>
       </c>
@@ -23096,7 +23106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="477" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
         <v>45</v>
       </c>
@@ -23140,7 +23150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
         <v>45</v>
       </c>
@@ -23184,7 +23194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="479" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
         <v>45</v>
       </c>
@@ -23228,7 +23238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="480" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
         <v>45</v>
       </c>
@@ -23272,7 +23282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
         <v>45</v>
       </c>
@@ -23316,7 +23326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
         <v>45</v>
       </c>
@@ -23360,7 +23370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
         <v>45</v>
       </c>
@@ -23404,7 +23414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
         <v>45</v>
       </c>
@@ -23448,7 +23458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
         <v>45</v>
       </c>
@@ -23492,7 +23502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
         <v>45</v>
       </c>
@@ -23536,7 +23546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
         <v>45</v>
       </c>
@@ -23580,7 +23590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="488" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
         <v>45</v>
       </c>
@@ -23624,7 +23634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
         <v>45</v>
       </c>
@@ -23668,7 +23678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
         <v>45</v>
       </c>
@@ -23712,7 +23722,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="491" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
         <v>45</v>
       </c>
@@ -23756,7 +23766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="492" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
         <v>45</v>
       </c>
@@ -23800,7 +23810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="493" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
         <v>45</v>
       </c>
@@ -23844,7 +23854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="494" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
         <v>45</v>
       </c>
@@ -23888,7 +23898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
         <v>45</v>
       </c>
@@ -23932,7 +23942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="496" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
         <v>45</v>
       </c>
@@ -23976,7 +23986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="497" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
         <v>45</v>
       </c>
@@ -24020,7 +24030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
         <v>45</v>
       </c>
@@ -24064,7 +24074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="499" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
         <v>45</v>
       </c>
@@ -24108,7 +24118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="500" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
         <v>45</v>
       </c>
@@ -24152,7 +24162,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="501" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
         <v>45</v>
       </c>
@@ -24196,7 +24206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
         <v>45</v>
       </c>
@@ -24240,7 +24250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
         <v>45</v>
       </c>
@@ -24284,7 +24294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
         <v>45</v>
       </c>
@@ -24328,7 +24338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="505" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
         <v>45</v>
       </c>
@@ -24372,7 +24382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
         <v>45</v>
       </c>
@@ -24416,7 +24426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
         <v>45</v>
       </c>
@@ -24460,7 +24470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="508" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
         <v>45</v>
       </c>
@@ -24504,7 +24514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="509" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
         <v>45</v>
       </c>
@@ -24548,7 +24558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
         <v>45</v>
       </c>
@@ -24592,7 +24602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
         <v>45</v>
       </c>
@@ -24636,7 +24646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
         <v>45</v>
       </c>
@@ -24680,7 +24690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
         <v>45</v>
       </c>
@@ -24724,7 +24734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
         <v>45</v>
       </c>
@@ -24768,7 +24778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
         <v>45</v>
       </c>
@@ -24812,7 +24822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
         <v>45</v>
       </c>
@@ -24856,7 +24866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
         <v>45</v>
       </c>
@@ -24900,7 +24910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
         <v>45</v>
       </c>
@@ -24944,7 +24954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
         <v>45</v>
       </c>
@@ -24988,7 +24998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
         <v>45</v>
       </c>
@@ -25032,7 +25042,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="521" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
         <v>45</v>
       </c>
@@ -25076,7 +25086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="s">
         <v>45</v>
       </c>
@@ -25120,7 +25130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
         <v>45</v>
       </c>
@@ -25164,7 +25174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="s">
         <v>45</v>
       </c>
@@ -25208,7 +25218,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="525" spans="1:14" ht="100" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="s">
         <v>45</v>
       </c>
@@ -25252,7 +25262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="s">
         <v>45</v>
       </c>
@@ -25296,7 +25306,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="527" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="s">
         <v>45</v>
       </c>
@@ -25340,7 +25350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1" t="s">
         <v>45</v>
       </c>
@@ -25384,7 +25394,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="529" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
         <v>46</v>
       </c>
@@ -25428,7 +25438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
         <v>46</v>
       </c>
@@ -25472,7 +25482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
         <v>46</v>
       </c>
@@ -25516,7 +25526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
         <v>46</v>
       </c>
@@ -25560,7 +25570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
         <v>46</v>
       </c>
@@ -25604,7 +25614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
         <v>46</v>
       </c>
@@ -25648,7 +25658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
         <v>46</v>
       </c>
@@ -25692,7 +25702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
         <v>46</v>
       </c>
@@ -25736,7 +25746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" spans="1:14" ht="87.5" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
         <v>46</v>
       </c>
@@ -25780,7 +25790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:14" ht="75" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
         <v>46</v>
       </c>
@@ -25824,7 +25834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:14" ht="62.5" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
         <v>46</v>
       </c>
@@ -25869,7 +25879,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:E1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="1.25" right="1.25" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25879,38 +25889,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="27.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="27.36328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.54296875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="27.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="22" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="21.453125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="21.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -25987,9 +25997,9 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>585</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -26064,7 +26074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -26141,7 +26151,7 @@
         <v>4.1666666666666664E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -26218,7 +26228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>34</v>
       </c>
@@ -26295,7 +26305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>35</v>
       </c>
@@ -26372,7 +26382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>36</v>
       </c>
@@ -26449,9 +26459,9 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>586</v>
       </c>
       <c r="B8">
         <v>61</v>
@@ -26526,9 +26536,9 @@
         <v>1.2096774193548387E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>587</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -26603,7 +26613,7 @@
         <v>2.8688524590163935E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>39</v>
       </c>
@@ -26680,7 +26690,7 @@
         <v>5.3571428571428568E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -26757,7 +26767,7 @@
         <v>3.5714285714285712E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -26834,7 +26844,7 @@
         <v>0.13846153846153847</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>42</v>
       </c>
@@ -26911,7 +26921,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>43</v>
       </c>
@@ -26988,7 +26998,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>44</v>
       </c>
@@ -27065,7 +27075,7 @@
         <v>1.0869565217391304E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -27142,7 +27152,7 @@
         <v>3.4482758620689655E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>46</v>
       </c>

--- a/Thesis/data/raw/autoic/coded-TedK_Longitudinal.xlsx
+++ b/Thesis/data/raw/autoic/coded-TedK_Longitudinal.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5b4dcdb2932ef22e/Documents/Integrative-Data-Project/Thesis/data/raw/autoic/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_22A9EB38F104CCB08B30471301005BB83B519864" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE7E005-D7BB-4A31-9B2B-39CC95F0733C}"/>
+  <xr:revisionPtr revIDLastSave="19" documentId="11_22A9EB38F104CCB08B30471301005BB83B519864" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D83F2252-01C3-4091-A385-B9B64329E64D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paragraph" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1131" uniqueCount="585">
   <si>
     <t>Document</t>
   </si>
@@ -119,9 +119,6 @@
     <t>ELAB_Integration_AllChunks</t>
   </si>
   <si>
-    <t>A Fantasy (1999)_1999.txt</t>
-  </si>
-  <si>
     <t>A Scientific American Article Theorizing a Tech Induced Apocalypse &amp; The Unabomber's Response_1993.txt</t>
   </si>
   <si>
@@ -135,12 +132,6 @@
   </si>
   <si>
     <t>Hit where it hurts_2002.txt</t>
-  </si>
-  <si>
-    <t>Morality and Revolution (1st Edition)_1999.txt</t>
-  </si>
-  <si>
-    <t>Morality and Revolution (3rd Edition)_2001.txt</t>
   </si>
   <si>
     <t>Progress versus Liberty_1972.txt</t>
@@ -1861,6 +1852,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2208,7 +2203,7 @@
     </row>
     <row r="2" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2217,7 +2212,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1">
         <v>75</v>
@@ -2252,7 +2247,7 @@
     </row>
     <row r="3" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B3" s="1">
         <v>2</v>
@@ -2261,7 +2256,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1">
         <v>75</v>
@@ -2296,7 +2291,7 @@
     </row>
     <row r="4" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B4" s="1">
         <v>3</v>
@@ -2305,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E4" s="1">
         <v>75</v>
@@ -2340,7 +2335,7 @@
     </row>
     <row r="5" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B5" s="1">
         <v>4</v>
@@ -2349,7 +2344,7 @@
         <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E5" s="1">
         <v>75</v>
@@ -2384,7 +2379,7 @@
     </row>
     <row r="6" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B6" s="1">
         <v>5</v>
@@ -2393,7 +2388,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E6" s="1">
         <v>75</v>
@@ -2428,7 +2423,7 @@
     </row>
     <row r="7" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B7" s="1">
         <v>6</v>
@@ -2437,7 +2432,7 @@
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1">
         <v>75</v>
@@ -2472,7 +2467,7 @@
     </row>
     <row r="8" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B8" s="1">
         <v>7</v>
@@ -2481,7 +2476,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E8" s="1">
         <v>75</v>
@@ -2516,7 +2511,7 @@
     </row>
     <row r="9" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B9" s="1">
         <v>8</v>
@@ -2525,7 +2520,7 @@
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1">
         <v>75</v>
@@ -2560,7 +2555,7 @@
     </row>
     <row r="10" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B10" s="1">
         <v>9</v>
@@ -2569,7 +2564,7 @@
         <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E10" s="1">
         <v>75</v>
@@ -2604,7 +2599,7 @@
     </row>
     <row r="11" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B11" s="1">
         <v>10</v>
@@ -2613,7 +2608,7 @@
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E11" s="1">
         <v>75</v>
@@ -2648,7 +2643,7 @@
     </row>
     <row r="12" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B12" s="1">
         <v>11</v>
@@ -2657,7 +2652,7 @@
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1">
         <v>75</v>
@@ -2692,7 +2687,7 @@
     </row>
     <row r="13" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B13" s="1">
         <v>12</v>
@@ -2701,7 +2696,7 @@
         <v>1</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E13" s="1">
         <v>75</v>
@@ -2736,7 +2731,7 @@
     </row>
     <row r="14" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B14" s="1">
         <v>13</v>
@@ -2745,7 +2740,7 @@
         <v>1</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E14" s="1">
         <v>75</v>
@@ -2780,7 +2775,7 @@
     </row>
     <row r="15" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B15" s="1">
         <v>14</v>
@@ -2789,7 +2784,7 @@
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1">
         <v>75</v>
@@ -2824,7 +2819,7 @@
     </row>
     <row r="16" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B16" s="1">
         <v>15</v>
@@ -2833,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E16" s="1">
         <v>75</v>
@@ -2868,7 +2863,7 @@
     </row>
     <row r="17" spans="1:14" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>582</v>
       </c>
       <c r="B17" s="1">
         <v>16</v>
@@ -2877,7 +2872,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E17" s="1">
         <v>22</v>
@@ -2912,7 +2907,7 @@
     </row>
     <row r="18" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B18" s="1">
         <v>1</v>
@@ -2921,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E18" s="1">
         <v>75</v>
@@ -2956,7 +2951,7 @@
     </row>
     <row r="19" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="1">
         <v>2</v>
@@ -2965,7 +2960,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E19" s="1">
         <v>75</v>
@@ -3000,7 +2995,7 @@
     </row>
     <row r="20" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B20" s="1">
         <v>3</v>
@@ -3009,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E20" s="1">
         <v>75</v>
@@ -3044,7 +3039,7 @@
     </row>
     <row r="21" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21" s="1">
         <v>4</v>
@@ -3053,7 +3048,7 @@
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E21" s="1">
         <v>75</v>
@@ -3088,7 +3083,7 @@
     </row>
     <row r="22" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B22" s="1">
         <v>5</v>
@@ -3097,7 +3092,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E22" s="1">
         <v>75</v>
@@ -3132,7 +3127,7 @@
     </row>
     <row r="23" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1">
         <v>6</v>
@@ -3141,7 +3136,7 @@
         <v>1</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E23" s="1">
         <v>75</v>
@@ -3176,7 +3171,7 @@
     </row>
     <row r="24" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1">
         <v>7</v>
@@ -3185,7 +3180,7 @@
         <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E24" s="1">
         <v>75</v>
@@ -3220,7 +3215,7 @@
     </row>
     <row r="25" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B25" s="1">
         <v>8</v>
@@ -3229,7 +3224,7 @@
         <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E25" s="1">
         <v>75</v>
@@ -3264,7 +3259,7 @@
     </row>
     <row r="26" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="1">
         <v>9</v>
@@ -3273,7 +3268,7 @@
         <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E26" s="1">
         <v>75</v>
@@ -3308,7 +3303,7 @@
     </row>
     <row r="27" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B27" s="1">
         <v>10</v>
@@ -3317,7 +3312,7 @@
         <v>1</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="E27" s="1">
         <v>75</v>
@@ -3352,7 +3347,7 @@
     </row>
     <row r="28" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="1">
         <v>11</v>
@@ -3361,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E28" s="1">
         <v>75</v>
@@ -3396,7 +3391,7 @@
     </row>
     <row r="29" spans="1:14" ht="127.5" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B29" s="1">
         <v>12</v>
@@ -3405,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E29" s="1">
         <v>2</v>
@@ -3440,7 +3435,7 @@
     </row>
     <row r="30" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B30" s="1">
         <v>1</v>
@@ -3449,7 +3444,7 @@
         <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E30" s="1">
         <v>75</v>
@@ -3484,7 +3479,7 @@
     </row>
     <row r="31" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="1">
         <v>2</v>
@@ -3493,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E31" s="1">
         <v>75</v>
@@ -3528,7 +3523,7 @@
     </row>
     <row r="32" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B32" s="1">
         <v>3</v>
@@ -3537,7 +3532,7 @@
         <v>1</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E32" s="1">
         <v>75</v>
@@ -3572,7 +3567,7 @@
     </row>
     <row r="33" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33" s="1">
         <v>4</v>
@@ -3581,7 +3576,7 @@
         <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E33" s="1">
         <v>75</v>
@@ -3616,7 +3611,7 @@
     </row>
     <row r="34" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B34" s="1">
         <v>5</v>
@@ -3625,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E34" s="1">
         <v>75</v>
@@ -3660,7 +3655,7 @@
     </row>
     <row r="35" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B35" s="1">
         <v>6</v>
@@ -3669,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E35" s="1">
         <v>75</v>
@@ -3704,7 +3699,7 @@
     </row>
     <row r="36" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" s="1">
         <v>7</v>
@@ -3713,7 +3708,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E36" s="1">
         <v>75</v>
@@ -3748,7 +3743,7 @@
     </row>
     <row r="37" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B37" s="1">
         <v>8</v>
@@ -3757,7 +3752,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E37" s="1">
         <v>75</v>
@@ -3792,7 +3787,7 @@
     </row>
     <row r="38" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B38" s="1">
         <v>9</v>
@@ -3801,7 +3796,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E38" s="1">
         <v>26</v>
@@ -3836,7 +3831,7 @@
     </row>
     <row r="39" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B39" s="1">
         <v>1</v>
@@ -3845,7 +3840,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E39" s="1">
         <v>75</v>
@@ -3880,7 +3875,7 @@
     </row>
     <row r="40" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B40" s="1">
         <v>2</v>
@@ -3889,7 +3884,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E40" s="1">
         <v>75</v>
@@ -3924,7 +3919,7 @@
     </row>
     <row r="41" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B41" s="1">
         <v>3</v>
@@ -3933,7 +3928,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E41" s="1">
         <v>75</v>
@@ -3968,7 +3963,7 @@
     </row>
     <row r="42" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B42" s="1">
         <v>4</v>
@@ -3977,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E42" s="1">
         <v>58</v>
@@ -4012,7 +4007,7 @@
     </row>
     <row r="43" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B43" s="1">
         <v>1</v>
@@ -4021,7 +4016,7 @@
         <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E43" s="1">
         <v>75</v>
@@ -4056,7 +4051,7 @@
     </row>
     <row r="44" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B44" s="1">
         <v>2</v>
@@ -4065,7 +4060,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E44" s="1">
         <v>75</v>
@@ -4100,7 +4095,7 @@
     </row>
     <row r="45" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B45" s="1">
         <v>3</v>
@@ -4109,7 +4104,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E45" s="1">
         <v>75</v>
@@ -4144,7 +4139,7 @@
     </row>
     <row r="46" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B46" s="1">
         <v>4</v>
@@ -4153,7 +4148,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E46" s="1">
         <v>75</v>
@@ -4188,7 +4183,7 @@
     </row>
     <row r="47" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B47" s="1">
         <v>5</v>
@@ -4197,7 +4192,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E47" s="1">
         <v>75</v>
@@ -4232,7 +4227,7 @@
     </row>
     <row r="48" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B48" s="1">
         <v>6</v>
@@ -4241,7 +4236,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E48" s="1">
         <v>75</v>
@@ -4276,7 +4271,7 @@
     </row>
     <row r="49" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B49" s="1">
         <v>7</v>
@@ -4285,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E49" s="1">
         <v>75</v>
@@ -4320,7 +4315,7 @@
     </row>
     <row r="50" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B50" s="1">
         <v>8</v>
@@ -4329,7 +4324,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E50" s="1">
         <v>75</v>
@@ -4364,7 +4359,7 @@
     </row>
     <row r="51" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B51" s="1">
         <v>9</v>
@@ -4373,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E51" s="1">
         <v>26</v>
@@ -4408,7 +4403,7 @@
     </row>
     <row r="52" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B52" s="1">
         <v>1</v>
@@ -4417,7 +4412,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E52" s="1">
         <v>75</v>
@@ -4452,7 +4447,7 @@
     </row>
     <row r="53" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B53" s="1">
         <v>2</v>
@@ -4461,7 +4456,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="E53" s="1">
         <v>75</v>
@@ -4496,7 +4491,7 @@
     </row>
     <row r="54" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B54" s="1">
         <v>3</v>
@@ -4505,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E54" s="1">
         <v>75</v>
@@ -4540,7 +4535,7 @@
     </row>
     <row r="55" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B55" s="1">
         <v>4</v>
@@ -4549,7 +4544,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E55" s="1">
         <v>75</v>
@@ -4584,7 +4579,7 @@
     </row>
     <row r="56" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B56" s="1">
         <v>5</v>
@@ -4593,7 +4588,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E56" s="1">
         <v>75</v>
@@ -4628,7 +4623,7 @@
     </row>
     <row r="57" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B57" s="1">
         <v>6</v>
@@ -4637,7 +4632,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E57" s="1">
         <v>75</v>
@@ -4672,7 +4667,7 @@
     </row>
     <row r="58" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B58" s="1">
         <v>7</v>
@@ -4681,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E58" s="1">
         <v>75</v>
@@ -4716,7 +4711,7 @@
     </row>
     <row r="59" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B59" s="1">
         <v>8</v>
@@ -4725,7 +4720,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="E59" s="1">
         <v>75</v>
@@ -4760,7 +4755,7 @@
     </row>
     <row r="60" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B60" s="1">
         <v>9</v>
@@ -4769,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E60" s="1">
         <v>75</v>
@@ -4804,7 +4799,7 @@
     </row>
     <row r="61" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B61" s="1">
         <v>10</v>
@@ -4813,7 +4808,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="E61" s="1">
         <v>75</v>
@@ -4848,7 +4843,7 @@
     </row>
     <row r="62" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B62" s="1">
         <v>11</v>
@@ -4857,7 +4852,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E62" s="1">
         <v>75</v>
@@ -4892,7 +4887,7 @@
     </row>
     <row r="63" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B63" s="1">
         <v>12</v>
@@ -4901,7 +4896,7 @@
         <v>1</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E63" s="1">
         <v>75</v>
@@ -4936,7 +4931,7 @@
     </row>
     <row r="64" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B64" s="1">
         <v>13</v>
@@ -4945,7 +4940,7 @@
         <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E64" s="1">
         <v>75</v>
@@ -4980,7 +4975,7 @@
     </row>
     <row r="65" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B65" s="1">
         <v>14</v>
@@ -4989,7 +4984,7 @@
         <v>1</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E65" s="1">
         <v>75</v>
@@ -5024,7 +5019,7 @@
     </row>
     <row r="66" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B66" s="1">
         <v>15</v>
@@ -5033,7 +5028,7 @@
         <v>1</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E66" s="1">
         <v>75</v>
@@ -5068,7 +5063,7 @@
     </row>
     <row r="67" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B67" s="1">
         <v>16</v>
@@ -5077,7 +5072,7 @@
         <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="E67" s="1">
         <v>75</v>
@@ -5112,7 +5107,7 @@
     </row>
     <row r="68" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B68" s="1">
         <v>17</v>
@@ -5121,7 +5116,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E68" s="1">
         <v>75</v>
@@ -5156,7 +5151,7 @@
     </row>
     <row r="69" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B69" s="1">
         <v>18</v>
@@ -5165,7 +5160,7 @@
         <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E69" s="1">
         <v>75</v>
@@ -5200,7 +5195,7 @@
     </row>
     <row r="70" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B70" s="1">
         <v>19</v>
@@ -5209,7 +5204,7 @@
         <v>1</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E70" s="1">
         <v>75</v>
@@ -5244,7 +5239,7 @@
     </row>
     <row r="71" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B71" s="1">
         <v>20</v>
@@ -5253,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E71" s="1">
         <v>75</v>
@@ -5288,7 +5283,7 @@
     </row>
     <row r="72" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B72" s="1">
         <v>21</v>
@@ -5297,7 +5292,7 @@
         <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E72" s="1">
         <v>75</v>
@@ -5332,7 +5327,7 @@
     </row>
     <row r="73" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B73" s="1">
         <v>22</v>
@@ -5341,7 +5336,7 @@
         <v>1</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="E73" s="1">
         <v>75</v>
@@ -5376,7 +5371,7 @@
     </row>
     <row r="74" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B74" s="1">
         <v>23</v>
@@ -5385,7 +5380,7 @@
         <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E74" s="1">
         <v>75</v>
@@ -5420,7 +5415,7 @@
     </row>
     <row r="75" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B75" s="1">
         <v>24</v>
@@ -5429,7 +5424,7 @@
         <v>1</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E75" s="1">
         <v>75</v>
@@ -5464,7 +5459,7 @@
     </row>
     <row r="76" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B76" s="1">
         <v>25</v>
@@ -5473,7 +5468,7 @@
         <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E76" s="1">
         <v>75</v>
@@ -5508,7 +5503,7 @@
     </row>
     <row r="77" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B77" s="1">
         <v>26</v>
@@ -5517,7 +5512,7 @@
         <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E77" s="1">
         <v>75</v>
@@ -5552,7 +5547,7 @@
     </row>
     <row r="78" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B78" s="1">
         <v>27</v>
@@ -5561,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E78" s="1">
         <v>75</v>
@@ -5596,7 +5591,7 @@
     </row>
     <row r="79" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B79" s="1">
         <v>28</v>
@@ -5605,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="E79" s="1">
         <v>75</v>
@@ -5640,7 +5635,7 @@
     </row>
     <row r="80" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B80" s="1">
         <v>29</v>
@@ -5649,7 +5644,7 @@
         <v>1</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E80" s="1">
         <v>75</v>
@@ -5684,7 +5679,7 @@
     </row>
     <row r="81" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B81" s="1">
         <v>30</v>
@@ -5693,7 +5688,7 @@
         <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E81" s="1">
         <v>75</v>
@@ -5728,7 +5723,7 @@
     </row>
     <row r="82" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B82" s="1">
         <v>31</v>
@@ -5737,7 +5732,7 @@
         <v>1</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E82" s="1">
         <v>75</v>
@@ -5772,7 +5767,7 @@
     </row>
     <row r="83" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B83" s="1">
         <v>32</v>
@@ -5781,7 +5776,7 @@
         <v>1</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E83" s="1">
         <v>75</v>
@@ -5816,7 +5811,7 @@
     </row>
     <row r="84" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B84" s="1">
         <v>33</v>
@@ -5825,7 +5820,7 @@
         <v>1</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E84" s="1">
         <v>75</v>
@@ -5860,7 +5855,7 @@
     </row>
     <row r="85" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B85" s="1">
         <v>34</v>
@@ -5869,7 +5864,7 @@
         <v>1</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="E85" s="1">
         <v>75</v>
@@ -5904,7 +5899,7 @@
     </row>
     <row r="86" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B86" s="1">
         <v>35</v>
@@ -5913,7 +5908,7 @@
         <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E86" s="1">
         <v>75</v>
@@ -5948,7 +5943,7 @@
     </row>
     <row r="87" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B87" s="1">
         <v>36</v>
@@ -5957,7 +5952,7 @@
         <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="E87" s="1">
         <v>75</v>
@@ -5992,7 +5987,7 @@
     </row>
     <row r="88" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B88" s="1">
         <v>37</v>
@@ -6001,7 +5996,7 @@
         <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E88" s="1">
         <v>75</v>
@@ -6036,7 +6031,7 @@
     </row>
     <row r="89" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B89" s="1">
         <v>38</v>
@@ -6045,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E89" s="1">
         <v>75</v>
@@ -6080,7 +6075,7 @@
     </row>
     <row r="90" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B90" s="1">
         <v>39</v>
@@ -6089,7 +6084,7 @@
         <v>1</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="E90" s="1">
         <v>75</v>
@@ -6124,7 +6119,7 @@
     </row>
     <row r="91" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B91" s="1">
         <v>40</v>
@@ -6133,7 +6128,7 @@
         <v>1</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E91" s="1">
         <v>75</v>
@@ -6168,7 +6163,7 @@
     </row>
     <row r="92" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B92" s="1">
         <v>41</v>
@@ -6177,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E92" s="1">
         <v>75</v>
@@ -6212,7 +6207,7 @@
     </row>
     <row r="93" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A93" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B93" s="1">
         <v>42</v>
@@ -6221,7 +6216,7 @@
         <v>1</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E93" s="1">
         <v>75</v>
@@ -6256,7 +6251,7 @@
     </row>
     <row r="94" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B94" s="1">
         <v>43</v>
@@ -6265,7 +6260,7 @@
         <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E94" s="1">
         <v>75</v>
@@ -6300,7 +6295,7 @@
     </row>
     <row r="95" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B95" s="1">
         <v>44</v>
@@ -6309,7 +6304,7 @@
         <v>1</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E95" s="1">
         <v>75</v>
@@ -6344,7 +6339,7 @@
     </row>
     <row r="96" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B96" s="1">
         <v>45</v>
@@ -6353,7 +6348,7 @@
         <v>1</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E96" s="1">
         <v>75</v>
@@ -6388,7 +6383,7 @@
     </row>
     <row r="97" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B97" s="1">
         <v>46</v>
@@ -6397,7 +6392,7 @@
         <v>1</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E97" s="1">
         <v>75</v>
@@ -6432,7 +6427,7 @@
     </row>
     <row r="98" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B98" s="1">
         <v>47</v>
@@ -6441,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="E98" s="1">
         <v>75</v>
@@ -6476,7 +6471,7 @@
     </row>
     <row r="99" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B99" s="1">
         <v>48</v>
@@ -6485,7 +6480,7 @@
         <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E99" s="1">
         <v>75</v>
@@ -6520,7 +6515,7 @@
     </row>
     <row r="100" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B100" s="1">
         <v>49</v>
@@ -6529,7 +6524,7 @@
         <v>1</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E100" s="1">
         <v>75</v>
@@ -6564,7 +6559,7 @@
     </row>
     <row r="101" spans="1:14" ht="25.5" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B101" s="1">
         <v>50</v>
@@ -6573,7 +6568,7 @@
         <v>0</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E101" s="1">
         <v>13</v>
@@ -6608,7 +6603,7 @@
     </row>
     <row r="102" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A102" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B102" s="1">
         <v>1</v>
@@ -6617,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E102" s="1">
         <v>75</v>
@@ -6652,7 +6647,7 @@
     </row>
     <row r="103" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B103" s="1">
         <v>2</v>
@@ -6661,7 +6656,7 @@
         <v>1</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E103" s="1">
         <v>75</v>
@@ -6696,7 +6691,7 @@
     </row>
     <row r="104" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B104" s="1">
         <v>3</v>
@@ -6705,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E104" s="1">
         <v>75</v>
@@ -6740,7 +6735,7 @@
     </row>
     <row r="105" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B105" s="1">
         <v>4</v>
@@ -6749,7 +6744,7 @@
         <v>1</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E105" s="1">
         <v>75</v>
@@ -6784,7 +6779,7 @@
     </row>
     <row r="106" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B106" s="1">
         <v>5</v>
@@ -6793,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="E106" s="1">
         <v>75</v>
@@ -6828,7 +6823,7 @@
     </row>
     <row r="107" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B107" s="1">
         <v>6</v>
@@ -6837,7 +6832,7 @@
         <v>1</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="E107" s="1">
         <v>75</v>
@@ -6872,7 +6867,7 @@
     </row>
     <row r="108" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B108" s="1">
         <v>7</v>
@@ -6881,7 +6876,7 @@
         <v>1</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E108" s="1">
         <v>75</v>
@@ -6916,7 +6911,7 @@
     </row>
     <row r="109" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B109" s="1">
         <v>8</v>
@@ -6925,7 +6920,7 @@
         <v>1</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E109" s="1">
         <v>75</v>
@@ -6960,7 +6955,7 @@
     </row>
     <row r="110" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B110" s="1">
         <v>9</v>
@@ -6969,7 +6964,7 @@
         <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E110" s="1">
         <v>75</v>
@@ -7004,7 +6999,7 @@
     </row>
     <row r="111" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B111" s="1">
         <v>10</v>
@@ -7013,7 +7008,7 @@
         <v>1</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E111" s="1">
         <v>75</v>
@@ -7048,7 +7043,7 @@
     </row>
     <row r="112" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B112" s="1">
         <v>11</v>
@@ -7057,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E112" s="1">
         <v>75</v>
@@ -7092,7 +7087,7 @@
     </row>
     <row r="113" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B113" s="1">
         <v>12</v>
@@ -7101,7 +7096,7 @@
         <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E113" s="1">
         <v>75</v>
@@ -7136,7 +7131,7 @@
     </row>
     <row r="114" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B114" s="1">
         <v>13</v>
@@ -7145,7 +7140,7 @@
         <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E114" s="1">
         <v>75</v>
@@ -7180,7 +7175,7 @@
     </row>
     <row r="115" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B115" s="1">
         <v>14</v>
@@ -7189,7 +7184,7 @@
         <v>1</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E115" s="1">
         <v>75</v>
@@ -7224,7 +7219,7 @@
     </row>
     <row r="116" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A116" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B116" s="1">
         <v>15</v>
@@ -7233,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E116" s="1">
         <v>75</v>
@@ -7268,7 +7263,7 @@
     </row>
     <row r="117" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B117" s="1">
         <v>16</v>
@@ -7277,7 +7272,7 @@
         <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E117" s="1">
         <v>75</v>
@@ -7312,7 +7307,7 @@
     </row>
     <row r="118" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B118" s="1">
         <v>17</v>
@@ -7321,7 +7316,7 @@
         <v>1</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E118" s="1">
         <v>75</v>
@@ -7356,7 +7351,7 @@
     </row>
     <row r="119" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B119" s="1">
         <v>18</v>
@@ -7365,7 +7360,7 @@
         <v>1</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E119" s="1">
         <v>75</v>
@@ -7400,7 +7395,7 @@
     </row>
     <row r="120" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B120" s="1">
         <v>19</v>
@@ -7409,7 +7404,7 @@
         <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E120" s="1">
         <v>75</v>
@@ -7444,7 +7439,7 @@
     </row>
     <row r="121" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B121" s="1">
         <v>20</v>
@@ -7453,7 +7448,7 @@
         <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E121" s="1">
         <v>75</v>
@@ -7488,7 +7483,7 @@
     </row>
     <row r="122" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B122" s="1">
         <v>21</v>
@@ -7497,7 +7492,7 @@
         <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E122" s="1">
         <v>75</v>
@@ -7532,7 +7527,7 @@
     </row>
     <row r="123" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B123" s="1">
         <v>22</v>
@@ -7541,7 +7536,7 @@
         <v>1</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E123" s="1">
         <v>75</v>
@@ -7576,7 +7571,7 @@
     </row>
     <row r="124" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B124" s="1">
         <v>23</v>
@@ -7585,7 +7580,7 @@
         <v>1</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E124" s="1">
         <v>75</v>
@@ -7620,7 +7615,7 @@
     </row>
     <row r="125" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B125" s="1">
         <v>24</v>
@@ -7629,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E125" s="1">
         <v>75</v>
@@ -7664,7 +7659,7 @@
     </row>
     <row r="126" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B126" s="1">
         <v>25</v>
@@ -7673,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E126" s="1">
         <v>75</v>
@@ -7708,7 +7703,7 @@
     </row>
     <row r="127" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B127" s="1">
         <v>26</v>
@@ -7717,7 +7712,7 @@
         <v>1</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E127" s="1">
         <v>75</v>
@@ -7752,7 +7747,7 @@
     </row>
     <row r="128" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B128" s="1">
         <v>27</v>
@@ -7761,7 +7756,7 @@
         <v>1</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E128" s="1">
         <v>75</v>
@@ -7796,7 +7791,7 @@
     </row>
     <row r="129" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B129" s="1">
         <v>28</v>
@@ -7805,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E129" s="1">
         <v>75</v>
@@ -7840,7 +7835,7 @@
     </row>
     <row r="130" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B130" s="1">
         <v>29</v>
@@ -7849,7 +7844,7 @@
         <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E130" s="1">
         <v>75</v>
@@ -7884,7 +7879,7 @@
     </row>
     <row r="131" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B131" s="1">
         <v>30</v>
@@ -7893,7 +7888,7 @@
         <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E131" s="1">
         <v>75</v>
@@ -7928,7 +7923,7 @@
     </row>
     <row r="132" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B132" s="1">
         <v>31</v>
@@ -7937,7 +7932,7 @@
         <v>1</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E132" s="1">
         <v>75</v>
@@ -7972,7 +7967,7 @@
     </row>
     <row r="133" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B133" s="1">
         <v>32</v>
@@ -7981,7 +7976,7 @@
         <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E133" s="1">
         <v>75</v>
@@ -8016,7 +8011,7 @@
     </row>
     <row r="134" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B134" s="1">
         <v>33</v>
@@ -8025,7 +8020,7 @@
         <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E134" s="1">
         <v>75</v>
@@ -8060,7 +8055,7 @@
     </row>
     <row r="135" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B135" s="1">
         <v>34</v>
@@ -8069,7 +8064,7 @@
         <v>1</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E135" s="1">
         <v>75</v>
@@ -8104,7 +8099,7 @@
     </row>
     <row r="136" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A136" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B136" s="1">
         <v>35</v>
@@ -8113,7 +8108,7 @@
         <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E136" s="1">
         <v>75</v>
@@ -8148,7 +8143,7 @@
     </row>
     <row r="137" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B137" s="1">
         <v>36</v>
@@ -8157,7 +8152,7 @@
         <v>1</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E137" s="1">
         <v>75</v>
@@ -8192,7 +8187,7 @@
     </row>
     <row r="138" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B138" s="1">
         <v>37</v>
@@ -8201,7 +8196,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E138" s="1">
         <v>75</v>
@@ -8236,7 +8231,7 @@
     </row>
     <row r="139" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A139" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B139" s="1">
         <v>38</v>
@@ -8245,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E139" s="1">
         <v>75</v>
@@ -8280,7 +8275,7 @@
     </row>
     <row r="140" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A140" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B140" s="1">
         <v>39</v>
@@ -8289,7 +8284,7 @@
         <v>1</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E140" s="1">
         <v>75</v>
@@ -8324,7 +8319,7 @@
     </row>
     <row r="141" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A141" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B141" s="1">
         <v>40</v>
@@ -8333,7 +8328,7 @@
         <v>1</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E141" s="1">
         <v>75</v>
@@ -8368,7 +8363,7 @@
     </row>
     <row r="142" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A142" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B142" s="1">
         <v>41</v>
@@ -8377,7 +8372,7 @@
         <v>1</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E142" s="1">
         <v>75</v>
@@ -8412,7 +8407,7 @@
     </row>
     <row r="143" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A143" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B143" s="1">
         <v>42</v>
@@ -8421,7 +8416,7 @@
         <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E143" s="1">
         <v>75</v>
@@ -8456,7 +8451,7 @@
     </row>
     <row r="144" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A144" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B144" s="1">
         <v>43</v>
@@ -8465,7 +8460,7 @@
         <v>1</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E144" s="1">
         <v>75</v>
@@ -8500,7 +8495,7 @@
     </row>
     <row r="145" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A145" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B145" s="1">
         <v>44</v>
@@ -8509,7 +8504,7 @@
         <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E145" s="1">
         <v>75</v>
@@ -8544,7 +8539,7 @@
     </row>
     <row r="146" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A146" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B146" s="1">
         <v>45</v>
@@ -8553,7 +8548,7 @@
         <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E146" s="1">
         <v>75</v>
@@ -8588,7 +8583,7 @@
     </row>
     <row r="147" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A147" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B147" s="1">
         <v>46</v>
@@ -8597,7 +8592,7 @@
         <v>1</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E147" s="1">
         <v>75</v>
@@ -8632,7 +8627,7 @@
     </row>
     <row r="148" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A148" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B148" s="1">
         <v>47</v>
@@ -8641,7 +8636,7 @@
         <v>1</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E148" s="1">
         <v>75</v>
@@ -8676,7 +8671,7 @@
     </row>
     <row r="149" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A149" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B149" s="1">
         <v>48</v>
@@ -8685,7 +8680,7 @@
         <v>1</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E149" s="1">
         <v>75</v>
@@ -8720,7 +8715,7 @@
     </row>
     <row r="150" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A150" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B150" s="1">
         <v>49</v>
@@ -8729,7 +8724,7 @@
         <v>1</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E150" s="1">
         <v>75</v>
@@ -8764,7 +8759,7 @@
     </row>
     <row r="151" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A151" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B151" s="1">
         <v>50</v>
@@ -8773,7 +8768,7 @@
         <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E151" s="1">
         <v>75</v>
@@ -8808,7 +8803,7 @@
     </row>
     <row r="152" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A152" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B152" s="1">
         <v>51</v>
@@ -8817,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E152" s="1">
         <v>75</v>
@@ -8852,7 +8847,7 @@
     </row>
     <row r="153" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A153" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B153" s="1">
         <v>52</v>
@@ -8861,7 +8856,7 @@
         <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E153" s="1">
         <v>75</v>
@@ -8896,7 +8891,7 @@
     </row>
     <row r="154" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A154" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B154" s="1">
         <v>53</v>
@@ -8905,7 +8900,7 @@
         <v>1</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E154" s="1">
         <v>75</v>
@@ -8940,7 +8935,7 @@
     </row>
     <row r="155" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A155" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B155" s="1">
         <v>54</v>
@@ -8949,7 +8944,7 @@
         <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E155" s="1">
         <v>75</v>
@@ -8984,7 +8979,7 @@
     </row>
     <row r="156" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B156" s="1">
         <v>55</v>
@@ -8993,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E156" s="1">
         <v>75</v>
@@ -9028,7 +9023,7 @@
     </row>
     <row r="157" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A157" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B157" s="1">
         <v>56</v>
@@ -9037,7 +9032,7 @@
         <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E157" s="1">
         <v>75</v>
@@ -9072,7 +9067,7 @@
     </row>
     <row r="158" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B158" s="1">
         <v>57</v>
@@ -9081,7 +9076,7 @@
         <v>1</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E158" s="1">
         <v>75</v>
@@ -9116,7 +9111,7 @@
     </row>
     <row r="159" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B159" s="1">
         <v>58</v>
@@ -9125,7 +9120,7 @@
         <v>1</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E159" s="1">
         <v>75</v>
@@ -9160,7 +9155,7 @@
     </row>
     <row r="160" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B160" s="1">
         <v>59</v>
@@ -9169,7 +9164,7 @@
         <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E160" s="1">
         <v>75</v>
@@ -9204,7 +9199,7 @@
     </row>
     <row r="161" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B161" s="1">
         <v>60</v>
@@ -9213,7 +9208,7 @@
         <v>1</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E161" s="1">
         <v>75</v>
@@ -9248,7 +9243,7 @@
     </row>
     <row r="162" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B162" s="1">
         <v>61</v>
@@ -9257,7 +9252,7 @@
         <v>1</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E162" s="1">
         <v>75</v>
@@ -9292,7 +9287,7 @@
     </row>
     <row r="163" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>37</v>
+        <v>583</v>
       </c>
       <c r="B163" s="1">
         <v>62</v>
@@ -9301,7 +9296,7 @@
         <v>0</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E163" s="1">
         <v>5</v>
@@ -9336,7 +9331,7 @@
     </row>
     <row r="164" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B164" s="1">
         <v>1</v>
@@ -9345,7 +9340,7 @@
         <v>1</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E164" s="1">
         <v>75</v>
@@ -9380,7 +9375,7 @@
     </row>
     <row r="165" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B165" s="1">
         <v>2</v>
@@ -9389,7 +9384,7 @@
         <v>1</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E165" s="1">
         <v>75</v>
@@ -9424,7 +9419,7 @@
     </row>
     <row r="166" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B166" s="1">
         <v>3</v>
@@ -9433,7 +9428,7 @@
         <v>1</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E166" s="1">
         <v>75</v>
@@ -9468,7 +9463,7 @@
     </row>
     <row r="167" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B167" s="1">
         <v>4</v>
@@ -9477,7 +9472,7 @@
         <v>1</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E167" s="1">
         <v>75</v>
@@ -9512,7 +9507,7 @@
     </row>
     <row r="168" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B168" s="1">
         <v>5</v>
@@ -9521,7 +9516,7 @@
         <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E168" s="1">
         <v>75</v>
@@ -9556,7 +9551,7 @@
     </row>
     <row r="169" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B169" s="1">
         <v>6</v>
@@ -9565,7 +9560,7 @@
         <v>1</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E169" s="1">
         <v>75</v>
@@ -9600,7 +9595,7 @@
     </row>
     <row r="170" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B170" s="1">
         <v>7</v>
@@ -9609,7 +9604,7 @@
         <v>1</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E170" s="1">
         <v>75</v>
@@ -9644,7 +9639,7 @@
     </row>
     <row r="171" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B171" s="1">
         <v>8</v>
@@ -9653,7 +9648,7 @@
         <v>1</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E171" s="1">
         <v>75</v>
@@ -9688,7 +9683,7 @@
     </row>
     <row r="172" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B172" s="1">
         <v>9</v>
@@ -9697,7 +9692,7 @@
         <v>1</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E172" s="1">
         <v>75</v>
@@ -9732,7 +9727,7 @@
     </row>
     <row r="173" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B173" s="1">
         <v>10</v>
@@ -9741,7 +9736,7 @@
         <v>1</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E173" s="1">
         <v>75</v>
@@ -9776,7 +9771,7 @@
     </row>
     <row r="174" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B174" s="1">
         <v>11</v>
@@ -9785,7 +9780,7 @@
         <v>1</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E174" s="1">
         <v>75</v>
@@ -9820,7 +9815,7 @@
     </row>
     <row r="175" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B175" s="1">
         <v>12</v>
@@ -9829,7 +9824,7 @@
         <v>1</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E175" s="1">
         <v>75</v>
@@ -9864,7 +9859,7 @@
     </row>
     <row r="176" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A176" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B176" s="1">
         <v>13</v>
@@ -9873,7 +9868,7 @@
         <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E176" s="1">
         <v>75</v>
@@ -9908,7 +9903,7 @@
     </row>
     <row r="177" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B177" s="1">
         <v>14</v>
@@ -9917,7 +9912,7 @@
         <v>1</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E177" s="1">
         <v>75</v>
@@ -9952,7 +9947,7 @@
     </row>
     <row r="178" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B178" s="1">
         <v>15</v>
@@ -9961,7 +9956,7 @@
         <v>1</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E178" s="1">
         <v>75</v>
@@ -9996,7 +9991,7 @@
     </row>
     <row r="179" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A179" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B179" s="1">
         <v>16</v>
@@ -10005,7 +10000,7 @@
         <v>1</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E179" s="1">
         <v>75</v>
@@ -10040,7 +10035,7 @@
     </row>
     <row r="180" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B180" s="1">
         <v>17</v>
@@ -10049,7 +10044,7 @@
         <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E180" s="1">
         <v>75</v>
@@ -10084,7 +10079,7 @@
     </row>
     <row r="181" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A181" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B181" s="1">
         <v>18</v>
@@ -10093,7 +10088,7 @@
         <v>1</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E181" s="1">
         <v>75</v>
@@ -10128,7 +10123,7 @@
     </row>
     <row r="182" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B182" s="1">
         <v>19</v>
@@ -10137,7 +10132,7 @@
         <v>1</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E182" s="1">
         <v>75</v>
@@ -10172,7 +10167,7 @@
     </row>
     <row r="183" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B183" s="1">
         <v>20</v>
@@ -10181,7 +10176,7 @@
         <v>1</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E183" s="1">
         <v>75</v>
@@ -10216,7 +10211,7 @@
     </row>
     <row r="184" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B184" s="1">
         <v>21</v>
@@ -10225,7 +10220,7 @@
         <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E184" s="1">
         <v>75</v>
@@ -10260,7 +10255,7 @@
     </row>
     <row r="185" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B185" s="1">
         <v>22</v>
@@ -10269,7 +10264,7 @@
         <v>1</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E185" s="1">
         <v>75</v>
@@ -10304,7 +10299,7 @@
     </row>
     <row r="186" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A186" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B186" s="1">
         <v>23</v>
@@ -10313,7 +10308,7 @@
         <v>1</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E186" s="1">
         <v>75</v>
@@ -10348,7 +10343,7 @@
     </row>
     <row r="187" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A187" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B187" s="1">
         <v>24</v>
@@ -10357,7 +10352,7 @@
         <v>1</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E187" s="1">
         <v>75</v>
@@ -10392,7 +10387,7 @@
     </row>
     <row r="188" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B188" s="1">
         <v>25</v>
@@ -10401,7 +10396,7 @@
         <v>1</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E188" s="1">
         <v>75</v>
@@ -10436,7 +10431,7 @@
     </row>
     <row r="189" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A189" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B189" s="1">
         <v>26</v>
@@ -10445,7 +10440,7 @@
         <v>1</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E189" s="1">
         <v>75</v>
@@ -10480,7 +10475,7 @@
     </row>
     <row r="190" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A190" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B190" s="1">
         <v>27</v>
@@ -10489,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E190" s="1">
         <v>75</v>
@@ -10524,7 +10519,7 @@
     </row>
     <row r="191" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A191" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B191" s="1">
         <v>28</v>
@@ -10533,7 +10528,7 @@
         <v>1</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E191" s="1">
         <v>75</v>
@@ -10568,7 +10563,7 @@
     </row>
     <row r="192" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B192" s="1">
         <v>29</v>
@@ -10577,7 +10572,7 @@
         <v>1</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E192" s="1">
         <v>75</v>
@@ -10612,7 +10607,7 @@
     </row>
     <row r="193" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B193" s="1">
         <v>30</v>
@@ -10621,7 +10616,7 @@
         <v>1</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E193" s="1">
         <v>75</v>
@@ -10656,7 +10651,7 @@
     </row>
     <row r="194" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B194" s="1">
         <v>31</v>
@@ -10665,7 +10660,7 @@
         <v>1</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E194" s="1">
         <v>75</v>
@@ -10700,7 +10695,7 @@
     </row>
     <row r="195" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A195" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B195" s="1">
         <v>32</v>
@@ -10709,7 +10704,7 @@
         <v>1</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E195" s="1">
         <v>75</v>
@@ -10744,7 +10739,7 @@
     </row>
     <row r="196" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A196" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B196" s="1">
         <v>33</v>
@@ -10753,7 +10748,7 @@
         <v>1</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E196" s="1">
         <v>75</v>
@@ -10788,7 +10783,7 @@
     </row>
     <row r="197" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A197" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B197" s="1">
         <v>34</v>
@@ -10797,7 +10792,7 @@
         <v>1</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E197" s="1">
         <v>75</v>
@@ -10832,7 +10827,7 @@
     </row>
     <row r="198" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A198" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B198" s="1">
         <v>35</v>
@@ -10841,7 +10836,7 @@
         <v>1</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E198" s="1">
         <v>75</v>
@@ -10876,7 +10871,7 @@
     </row>
     <row r="199" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A199" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B199" s="1">
         <v>36</v>
@@ -10885,7 +10880,7 @@
         <v>1</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E199" s="1">
         <v>75</v>
@@ -10920,7 +10915,7 @@
     </row>
     <row r="200" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A200" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B200" s="1">
         <v>37</v>
@@ -10929,7 +10924,7 @@
         <v>1</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E200" s="1">
         <v>75</v>
@@ -10964,7 +10959,7 @@
     </row>
     <row r="201" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B201" s="1">
         <v>38</v>
@@ -10973,7 +10968,7 @@
         <v>1</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E201" s="1">
         <v>75</v>
@@ -11008,7 +11003,7 @@
     </row>
     <row r="202" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B202" s="1">
         <v>39</v>
@@ -11017,7 +11012,7 @@
         <v>1</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E202" s="1">
         <v>75</v>
@@ -11052,7 +11047,7 @@
     </row>
     <row r="203" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B203" s="1">
         <v>40</v>
@@ -11061,7 +11056,7 @@
         <v>1</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E203" s="1">
         <v>75</v>
@@ -11096,7 +11091,7 @@
     </row>
     <row r="204" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B204" s="1">
         <v>41</v>
@@ -11105,7 +11100,7 @@
         <v>1</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E204" s="1">
         <v>75</v>
@@ -11140,7 +11135,7 @@
     </row>
     <row r="205" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A205" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B205" s="1">
         <v>42</v>
@@ -11149,7 +11144,7 @@
         <v>1</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E205" s="1">
         <v>75</v>
@@ -11184,7 +11179,7 @@
     </row>
     <row r="206" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A206" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B206" s="1">
         <v>43</v>
@@ -11193,7 +11188,7 @@
         <v>1</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E206" s="1">
         <v>75</v>
@@ -11228,7 +11223,7 @@
     </row>
     <row r="207" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B207" s="1">
         <v>44</v>
@@ -11237,7 +11232,7 @@
         <v>1</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E207" s="1">
         <v>75</v>
@@ -11272,7 +11267,7 @@
     </row>
     <row r="208" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A208" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B208" s="1">
         <v>45</v>
@@ -11281,7 +11276,7 @@
         <v>1</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="E208" s="1">
         <v>75</v>
@@ -11316,7 +11311,7 @@
     </row>
     <row r="209" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A209" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B209" s="1">
         <v>46</v>
@@ -11325,7 +11320,7 @@
         <v>1</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E209" s="1">
         <v>75</v>
@@ -11360,7 +11355,7 @@
     </row>
     <row r="210" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A210" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B210" s="1">
         <v>47</v>
@@ -11369,7 +11364,7 @@
         <v>1</v>
       </c>
       <c r="D210" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="E210" s="1">
         <v>75</v>
@@ -11404,7 +11399,7 @@
     </row>
     <row r="211" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B211" s="1">
         <v>48</v>
@@ -11413,7 +11408,7 @@
         <v>1</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E211" s="1">
         <v>75</v>
@@ -11448,7 +11443,7 @@
     </row>
     <row r="212" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A212" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B212" s="1">
         <v>49</v>
@@ -11457,7 +11452,7 @@
         <v>1</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="E212" s="1">
         <v>75</v>
@@ -11492,7 +11487,7 @@
     </row>
     <row r="213" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B213" s="1">
         <v>50</v>
@@ -11501,7 +11496,7 @@
         <v>1</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E213" s="1">
         <v>75</v>
@@ -11536,7 +11531,7 @@
     </row>
     <row r="214" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B214" s="1">
         <v>51</v>
@@ -11545,7 +11540,7 @@
         <v>1</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="E214" s="1">
         <v>75</v>
@@ -11580,7 +11575,7 @@
     </row>
     <row r="215" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A215" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B215" s="1">
         <v>52</v>
@@ -11589,7 +11584,7 @@
         <v>1</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E215" s="1">
         <v>75</v>
@@ -11624,7 +11619,7 @@
     </row>
     <row r="216" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B216" s="1">
         <v>53</v>
@@ -11633,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E216" s="1">
         <v>75</v>
@@ -11668,7 +11663,7 @@
     </row>
     <row r="217" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B217" s="1">
         <v>54</v>
@@ -11677,7 +11672,7 @@
         <v>1</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="E217" s="1">
         <v>75</v>
@@ -11712,7 +11707,7 @@
     </row>
     <row r="218" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B218" s="1">
         <v>55</v>
@@ -11721,7 +11716,7 @@
         <v>1</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="E218" s="1">
         <v>75</v>
@@ -11756,7 +11751,7 @@
     </row>
     <row r="219" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B219" s="1">
         <v>56</v>
@@ -11765,7 +11760,7 @@
         <v>1</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="E219" s="1">
         <v>75</v>
@@ -11800,7 +11795,7 @@
     </row>
     <row r="220" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B220" s="1">
         <v>57</v>
@@ -11809,7 +11804,7 @@
         <v>1</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E220" s="1">
         <v>75</v>
@@ -11844,7 +11839,7 @@
     </row>
     <row r="221" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B221" s="1">
         <v>58</v>
@@ -11853,7 +11848,7 @@
         <v>1</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="E221" s="1">
         <v>75</v>
@@ -11888,7 +11883,7 @@
     </row>
     <row r="222" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B222" s="1">
         <v>59</v>
@@ -11897,7 +11892,7 @@
         <v>1</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="E222" s="1">
         <v>75</v>
@@ -11932,7 +11927,7 @@
     </row>
     <row r="223" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A223" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B223" s="1">
         <v>60</v>
@@ -11941,7 +11936,7 @@
         <v>1</v>
       </c>
       <c r="D223" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="E223" s="1">
         <v>75</v>
@@ -11976,7 +11971,7 @@
     </row>
     <row r="224" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="B224" s="1">
         <v>61</v>
@@ -11985,7 +11980,7 @@
         <v>0</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="E224" s="1">
         <v>19</v>
@@ -12020,7 +12015,7 @@
     </row>
     <row r="225" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A225" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B225" s="1">
         <v>1</v>
@@ -12029,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="E225" s="1">
         <v>75</v>
@@ -12064,7 +12059,7 @@
     </row>
     <row r="226" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A226" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B226" s="1">
         <v>2</v>
@@ -12073,7 +12068,7 @@
         <v>1</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E226" s="1">
         <v>75</v>
@@ -12108,7 +12103,7 @@
     </row>
     <row r="227" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A227" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B227" s="1">
         <v>3</v>
@@ -12117,7 +12112,7 @@
         <v>1</v>
       </c>
       <c r="D227" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="E227" s="1">
         <v>75</v>
@@ -12152,7 +12147,7 @@
     </row>
     <row r="228" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A228" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B228" s="1">
         <v>4</v>
@@ -12161,7 +12156,7 @@
         <v>1</v>
       </c>
       <c r="D228" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="E228" s="1">
         <v>75</v>
@@ -12196,7 +12191,7 @@
     </row>
     <row r="229" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B229" s="1">
         <v>5</v>
@@ -12205,7 +12200,7 @@
         <v>1</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E229" s="1">
         <v>75</v>
@@ -12240,7 +12235,7 @@
     </row>
     <row r="230" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A230" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B230" s="1">
         <v>6</v>
@@ -12249,7 +12244,7 @@
         <v>1</v>
       </c>
       <c r="D230" s="1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E230" s="1">
         <v>75</v>
@@ -12284,7 +12279,7 @@
     </row>
     <row r="231" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A231" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B231" s="1">
         <v>7</v>
@@ -12293,7 +12288,7 @@
         <v>1</v>
       </c>
       <c r="D231" s="1" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="E231" s="1">
         <v>75</v>
@@ -12328,7 +12323,7 @@
     </row>
     <row r="232" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A232" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B232" s="1">
         <v>8</v>
@@ -12337,7 +12332,7 @@
         <v>1</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="E232" s="1">
         <v>75</v>
@@ -12372,7 +12367,7 @@
     </row>
     <row r="233" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A233" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B233" s="1">
         <v>9</v>
@@ -12381,7 +12376,7 @@
         <v>1</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="E233" s="1">
         <v>75</v>
@@ -12416,7 +12411,7 @@
     </row>
     <row r="234" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A234" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B234" s="1">
         <v>10</v>
@@ -12425,7 +12420,7 @@
         <v>1</v>
       </c>
       <c r="D234" s="1" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="E234" s="1">
         <v>75</v>
@@ -12460,7 +12455,7 @@
     </row>
     <row r="235" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B235" s="1">
         <v>11</v>
@@ -12469,7 +12464,7 @@
         <v>1</v>
       </c>
       <c r="D235" s="1" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="E235" s="1">
         <v>75</v>
@@ -12504,7 +12499,7 @@
     </row>
     <row r="236" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A236" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B236" s="1">
         <v>12</v>
@@ -12513,7 +12508,7 @@
         <v>1</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="E236" s="1">
         <v>75</v>
@@ -12548,7 +12543,7 @@
     </row>
     <row r="237" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A237" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B237" s="1">
         <v>13</v>
@@ -12557,7 +12552,7 @@
         <v>1</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="E237" s="1">
         <v>75</v>
@@ -12592,7 +12587,7 @@
     </row>
     <row r="238" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A238" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B238" s="1">
         <v>14</v>
@@ -12601,7 +12596,7 @@
         <v>1</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E238" s="1">
         <v>75</v>
@@ -12636,7 +12631,7 @@
     </row>
     <row r="239" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A239" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B239" s="1">
         <v>15</v>
@@ -12645,7 +12640,7 @@
         <v>1</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E239" s="1">
         <v>75</v>
@@ -12680,7 +12675,7 @@
     </row>
     <row r="240" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A240" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B240" s="1">
         <v>16</v>
@@ -12689,7 +12684,7 @@
         <v>1</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E240" s="1">
         <v>75</v>
@@ -12724,7 +12719,7 @@
     </row>
     <row r="241" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A241" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B241" s="1">
         <v>17</v>
@@ -12733,7 +12728,7 @@
         <v>1</v>
       </c>
       <c r="D241" s="1" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="E241" s="1">
         <v>75</v>
@@ -12768,7 +12763,7 @@
     </row>
     <row r="242" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A242" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B242" s="1">
         <v>18</v>
@@ -12777,7 +12772,7 @@
         <v>1</v>
       </c>
       <c r="D242" s="1" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="E242" s="1">
         <v>75</v>
@@ -12812,7 +12807,7 @@
     </row>
     <row r="243" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A243" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B243" s="1">
         <v>19</v>
@@ -12821,7 +12816,7 @@
         <v>1</v>
       </c>
       <c r="D243" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E243" s="1">
         <v>75</v>
@@ -12856,7 +12851,7 @@
     </row>
     <row r="244" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B244" s="1">
         <v>20</v>
@@ -12865,7 +12860,7 @@
         <v>1</v>
       </c>
       <c r="D244" s="1" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E244" s="1">
         <v>75</v>
@@ -12900,7 +12895,7 @@
     </row>
     <row r="245" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A245" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B245" s="1">
         <v>21</v>
@@ -12909,7 +12904,7 @@
         <v>1</v>
       </c>
       <c r="D245" s="1" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E245" s="1">
         <v>75</v>
@@ -12944,7 +12939,7 @@
     </row>
     <row r="246" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A246" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B246" s="1">
         <v>22</v>
@@ -12953,7 +12948,7 @@
         <v>1</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E246" s="1">
         <v>75</v>
@@ -12988,7 +12983,7 @@
     </row>
     <row r="247" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B247" s="1">
         <v>23</v>
@@ -12997,7 +12992,7 @@
         <v>1</v>
       </c>
       <c r="D247" s="1" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="E247" s="1">
         <v>75</v>
@@ -13032,7 +13027,7 @@
     </row>
     <row r="248" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A248" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B248" s="1">
         <v>24</v>
@@ -13041,7 +13036,7 @@
         <v>1</v>
       </c>
       <c r="D248" s="1" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="E248" s="1">
         <v>75</v>
@@ -13076,7 +13071,7 @@
     </row>
     <row r="249" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A249" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B249" s="1">
         <v>25</v>
@@ -13085,7 +13080,7 @@
         <v>1</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="E249" s="1">
         <v>75</v>
@@ -13120,7 +13115,7 @@
     </row>
     <row r="250" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B250" s="1">
         <v>26</v>
@@ -13129,7 +13124,7 @@
         <v>1</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E250" s="1">
         <v>75</v>
@@ -13164,7 +13159,7 @@
     </row>
     <row r="251" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A251" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B251" s="1">
         <v>27</v>
@@ -13173,7 +13168,7 @@
         <v>1</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="E251" s="1">
         <v>75</v>
@@ -13208,7 +13203,7 @@
     </row>
     <row r="252" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A252" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B252" s="1">
         <v>28</v>
@@ -13217,7 +13212,7 @@
         <v>1</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="E252" s="1">
         <v>75</v>
@@ -13252,7 +13247,7 @@
     </row>
     <row r="253" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A253" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B253" s="1">
         <v>29</v>
@@ -13261,7 +13256,7 @@
         <v>1</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E253" s="1">
         <v>75</v>
@@ -13296,7 +13291,7 @@
     </row>
     <row r="254" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A254" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B254" s="1">
         <v>30</v>
@@ -13305,7 +13300,7 @@
         <v>1</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E254" s="1">
         <v>75</v>
@@ -13340,7 +13335,7 @@
     </row>
     <row r="255" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A255" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B255" s="1">
         <v>31</v>
@@ -13349,7 +13344,7 @@
         <v>1</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E255" s="1">
         <v>75</v>
@@ -13384,7 +13379,7 @@
     </row>
     <row r="256" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A256" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B256" s="1">
         <v>32</v>
@@ -13393,7 +13388,7 @@
         <v>1</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E256" s="1">
         <v>75</v>
@@ -13428,7 +13423,7 @@
     </row>
     <row r="257" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A257" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B257" s="1">
         <v>33</v>
@@ -13437,7 +13432,7 @@
         <v>1</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="E257" s="1">
         <v>75</v>
@@ -13472,7 +13467,7 @@
     </row>
     <row r="258" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A258" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B258" s="1">
         <v>34</v>
@@ -13481,7 +13476,7 @@
         <v>1</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="E258" s="1">
         <v>75</v>
@@ -13516,7 +13511,7 @@
     </row>
     <row r="259" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A259" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B259" s="1">
         <v>35</v>
@@ -13525,7 +13520,7 @@
         <v>1</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="E259" s="1">
         <v>75</v>
@@ -13560,7 +13555,7 @@
     </row>
     <row r="260" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B260" s="1">
         <v>36</v>
@@ -13569,7 +13564,7 @@
         <v>1</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E260" s="1">
         <v>75</v>
@@ -13604,7 +13599,7 @@
     </row>
     <row r="261" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A261" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B261" s="1">
         <v>37</v>
@@ -13613,7 +13608,7 @@
         <v>1</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E261" s="1">
         <v>75</v>
@@ -13648,7 +13643,7 @@
     </row>
     <row r="262" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A262" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B262" s="1">
         <v>38</v>
@@ -13657,7 +13652,7 @@
         <v>1</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E262" s="1">
         <v>75</v>
@@ -13692,7 +13687,7 @@
     </row>
     <row r="263" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A263" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B263" s="1">
         <v>39</v>
@@ -13701,7 +13696,7 @@
         <v>1</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="E263" s="1">
         <v>75</v>
@@ -13736,7 +13731,7 @@
     </row>
     <row r="264" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A264" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B264" s="1">
         <v>40</v>
@@ -13745,7 +13740,7 @@
         <v>1</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="E264" s="1">
         <v>75</v>
@@ -13780,7 +13775,7 @@
     </row>
     <row r="265" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A265" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B265" s="1">
         <v>41</v>
@@ -13789,7 +13784,7 @@
         <v>1</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E265" s="1">
         <v>75</v>
@@ -13824,7 +13819,7 @@
     </row>
     <row r="266" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A266" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B266" s="1">
         <v>42</v>
@@ -13833,7 +13828,7 @@
         <v>1</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="E266" s="1">
         <v>75</v>
@@ -13868,7 +13863,7 @@
     </row>
     <row r="267" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A267" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B267" s="1">
         <v>43</v>
@@ -13877,7 +13872,7 @@
         <v>1</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="E267" s="1">
         <v>75</v>
@@ -13912,7 +13907,7 @@
     </row>
     <row r="268" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A268" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B268" s="1">
         <v>44</v>
@@ -13921,7 +13916,7 @@
         <v>1</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E268" s="1">
         <v>75</v>
@@ -13956,7 +13951,7 @@
     </row>
     <row r="269" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A269" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B269" s="1">
         <v>45</v>
@@ -13965,7 +13960,7 @@
         <v>1</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E269" s="1">
         <v>75</v>
@@ -14000,7 +13995,7 @@
     </row>
     <row r="270" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A270" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B270" s="1">
         <v>46</v>
@@ -14009,7 +14004,7 @@
         <v>1</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E270" s="1">
         <v>75</v>
@@ -14044,7 +14039,7 @@
     </row>
     <row r="271" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A271" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B271" s="1">
         <v>47</v>
@@ -14053,7 +14048,7 @@
         <v>1</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E271" s="1">
         <v>75</v>
@@ -14088,7 +14083,7 @@
     </row>
     <row r="272" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A272" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B272" s="1">
         <v>48</v>
@@ -14097,7 +14092,7 @@
         <v>1</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E272" s="1">
         <v>75</v>
@@ -14132,7 +14127,7 @@
     </row>
     <row r="273" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A273" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B273" s="1">
         <v>49</v>
@@ -14141,7 +14136,7 @@
         <v>1</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E273" s="1">
         <v>75</v>
@@ -14176,7 +14171,7 @@
     </row>
     <row r="274" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A274" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B274" s="1">
         <v>50</v>
@@ -14185,7 +14180,7 @@
         <v>1</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E274" s="1">
         <v>75</v>
@@ -14220,7 +14215,7 @@
     </row>
     <row r="275" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A275" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B275" s="1">
         <v>51</v>
@@ -14229,7 +14224,7 @@
         <v>1</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="E275" s="1">
         <v>75</v>
@@ -14264,7 +14259,7 @@
     </row>
     <row r="276" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A276" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B276" s="1">
         <v>52</v>
@@ -14273,7 +14268,7 @@
         <v>1</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E276" s="1">
         <v>75</v>
@@ -14308,7 +14303,7 @@
     </row>
     <row r="277" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A277" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B277" s="1">
         <v>53</v>
@@ -14317,7 +14312,7 @@
         <v>1</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E277" s="1">
         <v>75</v>
@@ -14352,7 +14347,7 @@
     </row>
     <row r="278" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A278" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B278" s="1">
         <v>54</v>
@@ -14361,7 +14356,7 @@
         <v>1</v>
       </c>
       <c r="D278" s="1" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E278" s="1">
         <v>75</v>
@@ -14396,7 +14391,7 @@
     </row>
     <row r="279" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A279" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B279" s="1">
         <v>55</v>
@@ -14405,7 +14400,7 @@
         <v>1</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="E279" s="1">
         <v>75</v>
@@ -14440,7 +14435,7 @@
     </row>
     <row r="280" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A280" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B280" s="1">
         <v>56</v>
@@ -14449,7 +14444,7 @@
         <v>1</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E280" s="1">
         <v>75</v>
@@ -14484,7 +14479,7 @@
     </row>
     <row r="281" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A281" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B281" s="1">
         <v>57</v>
@@ -14493,7 +14488,7 @@
         <v>1</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E281" s="1">
         <v>75</v>
@@ -14528,7 +14523,7 @@
     </row>
     <row r="282" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A282" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B282" s="1">
         <v>58</v>
@@ -14537,7 +14532,7 @@
         <v>1</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="E282" s="1">
         <v>75</v>
@@ -14572,7 +14567,7 @@
     </row>
     <row r="283" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A283" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B283" s="1">
         <v>59</v>
@@ -14581,7 +14576,7 @@
         <v>1</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E283" s="1">
         <v>75</v>
@@ -14616,7 +14611,7 @@
     </row>
     <row r="284" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A284" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B284" s="1">
         <v>60</v>
@@ -14625,7 +14620,7 @@
         <v>1</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="E284" s="1">
         <v>75</v>
@@ -14660,7 +14655,7 @@
     </row>
     <row r="285" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A285" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B285" s="1">
         <v>61</v>
@@ -14669,7 +14664,7 @@
         <v>1</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="E285" s="1">
         <v>75</v>
@@ -14704,7 +14699,7 @@
     </row>
     <row r="286" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A286" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B286" s="1">
         <v>62</v>
@@ -14713,7 +14708,7 @@
         <v>1</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="E286" s="1">
         <v>75</v>
@@ -14748,7 +14743,7 @@
     </row>
     <row r="287" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A287" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B287" s="1">
         <v>63</v>
@@ -14757,7 +14752,7 @@
         <v>1</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="E287" s="1">
         <v>75</v>
@@ -14792,7 +14787,7 @@
     </row>
     <row r="288" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A288" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B288" s="1">
         <v>64</v>
@@ -14801,7 +14796,7 @@
         <v>1</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="E288" s="1">
         <v>75</v>
@@ -14836,7 +14831,7 @@
     </row>
     <row r="289" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A289" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B289" s="1">
         <v>65</v>
@@ -14845,7 +14840,7 @@
         <v>1</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="E289" s="1">
         <v>75</v>
@@ -14880,7 +14875,7 @@
     </row>
     <row r="290" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A290" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B290" s="1">
         <v>66</v>
@@ -14889,7 +14884,7 @@
         <v>1</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E290" s="1">
         <v>75</v>
@@ -14924,7 +14919,7 @@
     </row>
     <row r="291" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A291" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B291" s="1">
         <v>67</v>
@@ -14933,7 +14928,7 @@
         <v>1</v>
       </c>
       <c r="D291" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E291" s="1">
         <v>75</v>
@@ -14968,7 +14963,7 @@
     </row>
     <row r="292" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A292" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B292" s="1">
         <v>68</v>
@@ -14977,7 +14972,7 @@
         <v>1</v>
       </c>
       <c r="D292" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E292" s="1">
         <v>75</v>
@@ -15012,7 +15007,7 @@
     </row>
     <row r="293" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A293" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B293" s="1">
         <v>69</v>
@@ -15021,7 +15016,7 @@
         <v>1</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E293" s="1">
         <v>75</v>
@@ -15056,7 +15051,7 @@
     </row>
     <row r="294" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A294" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B294" s="1">
         <v>70</v>
@@ -15065,7 +15060,7 @@
         <v>1</v>
       </c>
       <c r="D294" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E294" s="1">
         <v>75</v>
@@ -15100,7 +15095,7 @@
     </row>
     <row r="295" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B295" s="1">
         <v>71</v>
@@ -15109,7 +15104,7 @@
         <v>1</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E295" s="1">
         <v>75</v>
@@ -15144,7 +15139,7 @@
     </row>
     <row r="296" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A296" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B296" s="1">
         <v>72</v>
@@ -15153,7 +15148,7 @@
         <v>1</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E296" s="1">
         <v>75</v>
@@ -15188,7 +15183,7 @@
     </row>
     <row r="297" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A297" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B297" s="1">
         <v>73</v>
@@ -15197,7 +15192,7 @@
         <v>1</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E297" s="1">
         <v>75</v>
@@ -15232,7 +15227,7 @@
     </row>
     <row r="298" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A298" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B298" s="1">
         <v>74</v>
@@ -15241,7 +15236,7 @@
         <v>1</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="E298" s="1">
         <v>75</v>
@@ -15276,7 +15271,7 @@
     </row>
     <row r="299" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A299" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B299" s="1">
         <v>75</v>
@@ -15285,7 +15280,7 @@
         <v>1</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="E299" s="1">
         <v>75</v>
@@ -15320,7 +15315,7 @@
     </row>
     <row r="300" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A300" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B300" s="1">
         <v>76</v>
@@ -15329,7 +15324,7 @@
         <v>1</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E300" s="1">
         <v>75</v>
@@ -15364,7 +15359,7 @@
     </row>
     <row r="301" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A301" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B301" s="1">
         <v>77</v>
@@ -15373,7 +15368,7 @@
         <v>1</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E301" s="1">
         <v>75</v>
@@ -15408,7 +15403,7 @@
     </row>
     <row r="302" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A302" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B302" s="1">
         <v>78</v>
@@ -15417,7 +15412,7 @@
         <v>1</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="E302" s="1">
         <v>75</v>
@@ -15452,7 +15447,7 @@
     </row>
     <row r="303" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A303" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B303" s="1">
         <v>79</v>
@@ -15461,7 +15456,7 @@
         <v>1</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E303" s="1">
         <v>75</v>
@@ -15496,7 +15491,7 @@
     </row>
     <row r="304" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A304" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B304" s="1">
         <v>80</v>
@@ -15505,7 +15500,7 @@
         <v>1</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="E304" s="1">
         <v>75</v>
@@ -15540,7 +15535,7 @@
     </row>
     <row r="305" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A305" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B305" s="1">
         <v>81</v>
@@ -15549,7 +15544,7 @@
         <v>1</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E305" s="1">
         <v>75</v>
@@ -15584,7 +15579,7 @@
     </row>
     <row r="306" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A306" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B306" s="1">
         <v>82</v>
@@ -15593,7 +15588,7 @@
         <v>1</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E306" s="1">
         <v>75</v>
@@ -15628,7 +15623,7 @@
     </row>
     <row r="307" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A307" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B307" s="1">
         <v>83</v>
@@ -15637,7 +15632,7 @@
         <v>1</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E307" s="1">
         <v>75</v>
@@ -15672,7 +15667,7 @@
     </row>
     <row r="308" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A308" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B308" s="1">
         <v>84</v>
@@ -15681,7 +15676,7 @@
         <v>0</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="E308" s="1">
         <v>16</v>
@@ -15716,7 +15711,7 @@
     </row>
     <row r="309" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A309" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B309" s="1">
         <v>1</v>
@@ -15725,7 +15720,7 @@
         <v>1</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E309" s="1">
         <v>75</v>
@@ -15760,7 +15755,7 @@
     </row>
     <row r="310" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A310" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B310" s="1">
         <v>2</v>
@@ -15769,7 +15764,7 @@
         <v>1</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="E310" s="1">
         <v>75</v>
@@ -15804,7 +15799,7 @@
     </row>
     <row r="311" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A311" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B311" s="1">
         <v>3</v>
@@ -15813,7 +15808,7 @@
         <v>1</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E311" s="1">
         <v>75</v>
@@ -15848,7 +15843,7 @@
     </row>
     <row r="312" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A312" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B312" s="1">
         <v>4</v>
@@ -15857,7 +15852,7 @@
         <v>1</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E312" s="1">
         <v>75</v>
@@ -15892,7 +15887,7 @@
     </row>
     <row r="313" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A313" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B313" s="1">
         <v>5</v>
@@ -15901,7 +15896,7 @@
         <v>1</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E313" s="1">
         <v>75</v>
@@ -15936,7 +15931,7 @@
     </row>
     <row r="314" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A314" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B314" s="1">
         <v>6</v>
@@ -15945,7 +15940,7 @@
         <v>1</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="E314" s="1">
         <v>75</v>
@@ -15980,7 +15975,7 @@
     </row>
     <row r="315" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A315" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B315" s="1">
         <v>7</v>
@@ -15989,7 +15984,7 @@
         <v>1</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E315" s="1">
         <v>75</v>
@@ -16024,7 +16019,7 @@
     </row>
     <row r="316" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A316" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B316" s="1">
         <v>8</v>
@@ -16033,7 +16028,7 @@
         <v>1</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="E316" s="1">
         <v>75</v>
@@ -16068,7 +16063,7 @@
     </row>
     <row r="317" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A317" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B317" s="1">
         <v>9</v>
@@ -16077,7 +16072,7 @@
         <v>1</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E317" s="1">
         <v>75</v>
@@ -16112,7 +16107,7 @@
     </row>
     <row r="318" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A318" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B318" s="1">
         <v>10</v>
@@ -16121,7 +16116,7 @@
         <v>1</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E318" s="1">
         <v>75</v>
@@ -16156,7 +16151,7 @@
     </row>
     <row r="319" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A319" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B319" s="1">
         <v>11</v>
@@ -16165,7 +16160,7 @@
         <v>1</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E319" s="1">
         <v>75</v>
@@ -16200,7 +16195,7 @@
     </row>
     <row r="320" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A320" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B320" s="1">
         <v>12</v>
@@ -16209,7 +16204,7 @@
         <v>1</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="E320" s="1">
         <v>75</v>
@@ -16244,7 +16239,7 @@
     </row>
     <row r="321" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A321" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B321" s="1">
         <v>13</v>
@@ -16253,7 +16248,7 @@
         <v>1</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E321" s="1">
         <v>75</v>
@@ -16288,7 +16283,7 @@
     </row>
     <row r="322" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A322" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B322" s="1">
         <v>14</v>
@@ -16297,7 +16292,7 @@
         <v>1</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E322" s="1">
         <v>75</v>
@@ -16332,7 +16327,7 @@
     </row>
     <row r="323" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A323" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B323" s="1">
         <v>15</v>
@@ -16341,7 +16336,7 @@
         <v>1</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E323" s="1">
         <v>75</v>
@@ -16376,7 +16371,7 @@
     </row>
     <row r="324" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A324" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B324" s="1">
         <v>16</v>
@@ -16385,7 +16380,7 @@
         <v>1</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E324" s="1">
         <v>75</v>
@@ -16420,7 +16415,7 @@
     </row>
     <row r="325" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A325" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B325" s="1">
         <v>17</v>
@@ -16429,7 +16424,7 @@
         <v>1</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E325" s="1">
         <v>75</v>
@@ -16464,7 +16459,7 @@
     </row>
     <row r="326" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A326" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B326" s="1">
         <v>18</v>
@@ -16473,7 +16468,7 @@
         <v>1</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E326" s="1">
         <v>75</v>
@@ -16508,7 +16503,7 @@
     </row>
     <row r="327" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A327" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B327" s="1">
         <v>19</v>
@@ -16517,7 +16512,7 @@
         <v>1</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E327" s="1">
         <v>75</v>
@@ -16552,7 +16547,7 @@
     </row>
     <row r="328" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A328" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B328" s="1">
         <v>20</v>
@@ -16561,7 +16556,7 @@
         <v>1</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E328" s="1">
         <v>75</v>
@@ -16596,7 +16591,7 @@
     </row>
     <row r="329" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A329" s="1" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B329" s="1">
         <v>21</v>
@@ -16605,7 +16600,7 @@
         <v>0</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="E329" s="1">
         <v>34</v>
@@ -16640,7 +16635,7 @@
     </row>
     <row r="330" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A330" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B330" s="1">
         <v>1</v>
@@ -16649,7 +16644,7 @@
         <v>1</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E330" s="1">
         <v>75</v>
@@ -16684,7 +16679,7 @@
     </row>
     <row r="331" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A331" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B331" s="1">
         <v>2</v>
@@ -16693,7 +16688,7 @@
         <v>1</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E331" s="1">
         <v>75</v>
@@ -16728,7 +16723,7 @@
     </row>
     <row r="332" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A332" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B332" s="1">
         <v>3</v>
@@ -16737,7 +16732,7 @@
         <v>1</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="E332" s="1">
         <v>75</v>
@@ -16772,7 +16767,7 @@
     </row>
     <row r="333" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A333" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B333" s="1">
         <v>4</v>
@@ -16781,7 +16776,7 @@
         <v>1</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E333" s="1">
         <v>75</v>
@@ -16816,7 +16811,7 @@
     </row>
     <row r="334" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A334" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B334" s="1">
         <v>5</v>
@@ -16825,7 +16820,7 @@
         <v>1</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E334" s="1">
         <v>75</v>
@@ -16860,7 +16855,7 @@
     </row>
     <row r="335" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A335" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B335" s="1">
         <v>6</v>
@@ -16869,7 +16864,7 @@
         <v>1</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="E335" s="1">
         <v>75</v>
@@ -16904,7 +16899,7 @@
     </row>
     <row r="336" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A336" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B336" s="1">
         <v>7</v>
@@ -16913,7 +16908,7 @@
         <v>1</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E336" s="1">
         <v>75</v>
@@ -16948,7 +16943,7 @@
     </row>
     <row r="337" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A337" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B337" s="1">
         <v>8</v>
@@ -16957,7 +16952,7 @@
         <v>1</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E337" s="1">
         <v>75</v>
@@ -16992,7 +16987,7 @@
     </row>
     <row r="338" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A338" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B338" s="1">
         <v>9</v>
@@ -17001,7 +16996,7 @@
         <v>1</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="E338" s="1">
         <v>75</v>
@@ -17036,7 +17031,7 @@
     </row>
     <row r="339" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A339" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B339" s="1">
         <v>10</v>
@@ -17045,7 +17040,7 @@
         <v>1</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="E339" s="1">
         <v>75</v>
@@ -17080,7 +17075,7 @@
     </row>
     <row r="340" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A340" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B340" s="1">
         <v>11</v>
@@ -17089,7 +17084,7 @@
         <v>1</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="E340" s="1">
         <v>75</v>
@@ -17124,7 +17119,7 @@
     </row>
     <row r="341" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A341" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B341" s="1">
         <v>12</v>
@@ -17133,7 +17128,7 @@
         <v>1</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="E341" s="1">
         <v>75</v>
@@ -17168,7 +17163,7 @@
     </row>
     <row r="342" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A342" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B342" s="1">
         <v>13</v>
@@ -17177,7 +17172,7 @@
         <v>1</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E342" s="1">
         <v>75</v>
@@ -17212,7 +17207,7 @@
     </row>
     <row r="343" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A343" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B343" s="1">
         <v>14</v>
@@ -17221,7 +17216,7 @@
         <v>1</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E343" s="1">
         <v>75</v>
@@ -17256,7 +17251,7 @@
     </row>
     <row r="344" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A344" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B344" s="1">
         <v>15</v>
@@ -17265,7 +17260,7 @@
         <v>1</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E344" s="1">
         <v>75</v>
@@ -17300,7 +17295,7 @@
     </row>
     <row r="345" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A345" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B345" s="1">
         <v>16</v>
@@ -17309,7 +17304,7 @@
         <v>1</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="E345" s="1">
         <v>75</v>
@@ -17344,7 +17339,7 @@
     </row>
     <row r="346" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A346" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B346" s="1">
         <v>17</v>
@@ -17353,7 +17348,7 @@
         <v>1</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="E346" s="1">
         <v>75</v>
@@ -17388,7 +17383,7 @@
     </row>
     <row r="347" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A347" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B347" s="1">
         <v>18</v>
@@ -17397,7 +17392,7 @@
         <v>1</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E347" s="1">
         <v>75</v>
@@ -17432,7 +17427,7 @@
     </row>
     <row r="348" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A348" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B348" s="1">
         <v>19</v>
@@ -17441,7 +17436,7 @@
         <v>1</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="E348" s="1">
         <v>75</v>
@@ -17476,7 +17471,7 @@
     </row>
     <row r="349" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A349" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B349" s="1">
         <v>20</v>
@@ -17485,7 +17480,7 @@
         <v>1</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E349" s="1">
         <v>75</v>
@@ -17520,7 +17515,7 @@
     </row>
     <row r="350" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A350" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B350" s="1">
         <v>21</v>
@@ -17529,7 +17524,7 @@
         <v>1</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E350" s="1">
         <v>75</v>
@@ -17564,7 +17559,7 @@
     </row>
     <row r="351" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A351" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B351" s="1">
         <v>22</v>
@@ -17573,7 +17568,7 @@
         <v>1</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E351" s="1">
         <v>75</v>
@@ -17608,7 +17603,7 @@
     </row>
     <row r="352" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A352" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B352" s="1">
         <v>23</v>
@@ -17617,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="E352" s="1">
         <v>75</v>
@@ -17652,7 +17647,7 @@
     </row>
     <row r="353" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A353" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B353" s="1">
         <v>24</v>
@@ -17661,7 +17656,7 @@
         <v>1</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E353" s="1">
         <v>75</v>
@@ -17696,7 +17691,7 @@
     </row>
     <row r="354" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A354" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B354" s="1">
         <v>25</v>
@@ -17705,7 +17700,7 @@
         <v>1</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="E354" s="1">
         <v>75</v>
@@ -17740,7 +17735,7 @@
     </row>
     <row r="355" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A355" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B355" s="1">
         <v>26</v>
@@ -17749,7 +17744,7 @@
         <v>1</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="E355" s="1">
         <v>75</v>
@@ -17784,7 +17779,7 @@
     </row>
     <row r="356" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A356" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B356" s="1">
         <v>27</v>
@@ -17793,7 +17788,7 @@
         <v>1</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E356" s="1">
         <v>75</v>
@@ -17828,7 +17823,7 @@
     </row>
     <row r="357" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A357" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B357" s="1">
         <v>28</v>
@@ -17837,7 +17832,7 @@
         <v>1</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E357" s="1">
         <v>75</v>
@@ -17872,7 +17867,7 @@
     </row>
     <row r="358" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A358" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B358" s="1">
         <v>29</v>
@@ -17881,7 +17876,7 @@
         <v>1</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="E358" s="1">
         <v>75</v>
@@ -17916,7 +17911,7 @@
     </row>
     <row r="359" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A359" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B359" s="1">
         <v>30</v>
@@ -17925,7 +17920,7 @@
         <v>1</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E359" s="1">
         <v>75</v>
@@ -17960,7 +17955,7 @@
     </row>
     <row r="360" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A360" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B360" s="1">
         <v>31</v>
@@ -17969,7 +17964,7 @@
         <v>1</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E360" s="1">
         <v>75</v>
@@ -18004,7 +17999,7 @@
     </row>
     <row r="361" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A361" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B361" s="1">
         <v>32</v>
@@ -18013,7 +18008,7 @@
         <v>1</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E361" s="1">
         <v>75</v>
@@ -18048,7 +18043,7 @@
     </row>
     <row r="362" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A362" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B362" s="1">
         <v>33</v>
@@ -18057,7 +18052,7 @@
         <v>1</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E362" s="1">
         <v>75</v>
@@ -18092,7 +18087,7 @@
     </row>
     <row r="363" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A363" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B363" s="1">
         <v>34</v>
@@ -18101,7 +18096,7 @@
         <v>1</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E363" s="1">
         <v>75</v>
@@ -18136,7 +18131,7 @@
     </row>
     <row r="364" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A364" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B364" s="1">
         <v>35</v>
@@ -18145,7 +18140,7 @@
         <v>1</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="E364" s="1">
         <v>75</v>
@@ -18180,7 +18175,7 @@
     </row>
     <row r="365" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A365" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B365" s="1">
         <v>36</v>
@@ -18189,7 +18184,7 @@
         <v>1</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E365" s="1">
         <v>75</v>
@@ -18224,7 +18219,7 @@
     </row>
     <row r="366" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A366" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B366" s="1">
         <v>37</v>
@@ -18233,7 +18228,7 @@
         <v>1</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="E366" s="1">
         <v>75</v>
@@ -18268,7 +18263,7 @@
     </row>
     <row r="367" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A367" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B367" s="1">
         <v>38</v>
@@ -18277,7 +18272,7 @@
         <v>1</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E367" s="1">
         <v>75</v>
@@ -18312,7 +18307,7 @@
     </row>
     <row r="368" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A368" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B368" s="1">
         <v>39</v>
@@ -18321,7 +18316,7 @@
         <v>1</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E368" s="1">
         <v>75</v>
@@ -18356,7 +18351,7 @@
     </row>
     <row r="369" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A369" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B369" s="1">
         <v>40</v>
@@ -18365,7 +18360,7 @@
         <v>1</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="E369" s="1">
         <v>75</v>
@@ -18400,7 +18395,7 @@
     </row>
     <row r="370" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A370" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B370" s="1">
         <v>41</v>
@@ -18409,7 +18404,7 @@
         <v>1</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E370" s="1">
         <v>75</v>
@@ -18444,7 +18439,7 @@
     </row>
     <row r="371" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A371" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B371" s="1">
         <v>42</v>
@@ -18453,7 +18448,7 @@
         <v>1</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E371" s="1">
         <v>75</v>
@@ -18488,7 +18483,7 @@
     </row>
     <row r="372" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A372" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B372" s="1">
         <v>43</v>
@@ -18497,7 +18492,7 @@
         <v>1</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E372" s="1">
         <v>75</v>
@@ -18532,7 +18527,7 @@
     </row>
     <row r="373" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A373" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B373" s="1">
         <v>44</v>
@@ -18541,7 +18536,7 @@
         <v>1</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E373" s="1">
         <v>75</v>
@@ -18576,7 +18571,7 @@
     </row>
     <row r="374" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A374" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B374" s="1">
         <v>45</v>
@@ -18585,7 +18580,7 @@
         <v>1</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E374" s="1">
         <v>75</v>
@@ -18620,7 +18615,7 @@
     </row>
     <row r="375" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A375" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B375" s="1">
         <v>46</v>
@@ -18629,7 +18624,7 @@
         <v>1</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E375" s="1">
         <v>75</v>
@@ -18664,7 +18659,7 @@
     </row>
     <row r="376" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A376" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B376" s="1">
         <v>47</v>
@@ -18673,7 +18668,7 @@
         <v>1</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="E376" s="1">
         <v>75</v>
@@ -18708,7 +18703,7 @@
     </row>
     <row r="377" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A377" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B377" s="1">
         <v>48</v>
@@ -18717,7 +18712,7 @@
         <v>1</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E377" s="1">
         <v>75</v>
@@ -18752,7 +18747,7 @@
     </row>
     <row r="378" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A378" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B378" s="1">
         <v>49</v>
@@ -18761,7 +18756,7 @@
         <v>1</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E378" s="1">
         <v>75</v>
@@ -18796,7 +18791,7 @@
     </row>
     <row r="379" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A379" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B379" s="1">
         <v>50</v>
@@ -18805,7 +18800,7 @@
         <v>1</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E379" s="1">
         <v>75</v>
@@ -18840,7 +18835,7 @@
     </row>
     <row r="380" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A380" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B380" s="1">
         <v>51</v>
@@ -18849,7 +18844,7 @@
         <v>1</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E380" s="1">
         <v>75</v>
@@ -18884,7 +18879,7 @@
     </row>
     <row r="381" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A381" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B381" s="1">
         <v>52</v>
@@ -18893,7 +18888,7 @@
         <v>1</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E381" s="1">
         <v>75</v>
@@ -18928,7 +18923,7 @@
     </row>
     <row r="382" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A382" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B382" s="1">
         <v>53</v>
@@ -18937,7 +18932,7 @@
         <v>1</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="E382" s="1">
         <v>75</v>
@@ -18972,7 +18967,7 @@
     </row>
     <row r="383" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A383" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B383" s="1">
         <v>54</v>
@@ -18981,7 +18976,7 @@
         <v>1</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E383" s="1">
         <v>75</v>
@@ -19016,7 +19011,7 @@
     </row>
     <row r="384" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A384" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B384" s="1">
         <v>55</v>
@@ -19025,7 +19020,7 @@
         <v>1</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E384" s="1">
         <v>75</v>
@@ -19060,7 +19055,7 @@
     </row>
     <row r="385" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A385" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B385" s="1">
         <v>56</v>
@@ -19069,7 +19064,7 @@
         <v>1</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E385" s="1">
         <v>75</v>
@@ -19104,7 +19099,7 @@
     </row>
     <row r="386" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A386" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B386" s="1">
         <v>57</v>
@@ -19113,7 +19108,7 @@
         <v>1</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E386" s="1">
         <v>75</v>
@@ -19148,7 +19143,7 @@
     </row>
     <row r="387" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A387" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B387" s="1">
         <v>58</v>
@@ -19157,7 +19152,7 @@
         <v>1</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="E387" s="1">
         <v>75</v>
@@ -19192,7 +19187,7 @@
     </row>
     <row r="388" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A388" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B388" s="1">
         <v>59</v>
@@ -19201,7 +19196,7 @@
         <v>1</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="E388" s="1">
         <v>75</v>
@@ -19236,7 +19231,7 @@
     </row>
     <row r="389" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A389" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B389" s="1">
         <v>60</v>
@@ -19245,7 +19240,7 @@
         <v>1</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E389" s="1">
         <v>75</v>
@@ -19280,7 +19275,7 @@
     </row>
     <row r="390" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A390" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B390" s="1">
         <v>61</v>
@@ -19289,7 +19284,7 @@
         <v>1</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E390" s="1">
         <v>75</v>
@@ -19324,7 +19319,7 @@
     </row>
     <row r="391" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A391" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B391" s="1">
         <v>62</v>
@@ -19333,7 +19328,7 @@
         <v>1</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E391" s="1">
         <v>75</v>
@@ -19368,7 +19363,7 @@
     </row>
     <row r="392" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A392" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B392" s="1">
         <v>63</v>
@@ -19377,7 +19372,7 @@
         <v>1</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E392" s="1">
         <v>75</v>
@@ -19412,7 +19407,7 @@
     </row>
     <row r="393" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A393" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B393" s="1">
         <v>64</v>
@@ -19421,7 +19416,7 @@
         <v>1</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="E393" s="1">
         <v>75</v>
@@ -19456,7 +19451,7 @@
     </row>
     <row r="394" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A394" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B394" s="1">
         <v>65</v>
@@ -19465,7 +19460,7 @@
         <v>0</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="E394" s="1">
         <v>1</v>
@@ -19500,7 +19495,7 @@
     </row>
     <row r="395" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A395" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B395" s="1">
         <v>1</v>
@@ -19509,7 +19504,7 @@
         <v>1</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E395" s="1">
         <v>75</v>
@@ -19544,7 +19539,7 @@
     </row>
     <row r="396" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A396" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B396" s="1">
         <v>2</v>
@@ -19553,7 +19548,7 @@
         <v>1</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="E396" s="1">
         <v>75</v>
@@ -19588,7 +19583,7 @@
     </row>
     <row r="397" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A397" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B397" s="1">
         <v>3</v>
@@ -19597,7 +19592,7 @@
         <v>1</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="E397" s="1">
         <v>75</v>
@@ -19632,7 +19627,7 @@
     </row>
     <row r="398" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A398" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B398" s="1">
         <v>4</v>
@@ -19641,7 +19636,7 @@
         <v>1</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="E398" s="1">
         <v>75</v>
@@ -19676,7 +19671,7 @@
     </row>
     <row r="399" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A399" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B399" s="1">
         <v>5</v>
@@ -19685,7 +19680,7 @@
         <v>1</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E399" s="1">
         <v>75</v>
@@ -19720,7 +19715,7 @@
     </row>
     <row r="400" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A400" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B400" s="1">
         <v>6</v>
@@ -19729,7 +19724,7 @@
         <v>1</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="E400" s="1">
         <v>75</v>
@@ -19764,7 +19759,7 @@
     </row>
     <row r="401" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A401" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B401" s="1">
         <v>7</v>
@@ -19773,7 +19768,7 @@
         <v>1</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="E401" s="1">
         <v>75</v>
@@ -19808,7 +19803,7 @@
     </row>
     <row r="402" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A402" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B402" s="1">
         <v>8</v>
@@ -19817,7 +19812,7 @@
         <v>1</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="E402" s="1">
         <v>75</v>
@@ -19852,7 +19847,7 @@
     </row>
     <row r="403" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A403" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B403" s="1">
         <v>9</v>
@@ -19861,7 +19856,7 @@
         <v>1</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E403" s="1">
         <v>75</v>
@@ -19896,7 +19891,7 @@
     </row>
     <row r="404" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A404" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B404" s="1">
         <v>10</v>
@@ -19905,7 +19900,7 @@
         <v>1</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="E404" s="1">
         <v>75</v>
@@ -19940,7 +19935,7 @@
     </row>
     <row r="405" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A405" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B405" s="1">
         <v>11</v>
@@ -19949,7 +19944,7 @@
         <v>1</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="E405" s="1">
         <v>75</v>
@@ -19984,7 +19979,7 @@
     </row>
     <row r="406" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A406" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B406" s="1">
         <v>12</v>
@@ -19993,7 +19988,7 @@
         <v>1</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E406" s="1">
         <v>75</v>
@@ -20028,7 +20023,7 @@
     </row>
     <row r="407" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A407" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B407" s="1">
         <v>13</v>
@@ -20037,7 +20032,7 @@
         <v>1</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="E407" s="1">
         <v>75</v>
@@ -20072,7 +20067,7 @@
     </row>
     <row r="408" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A408" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B408" s="1">
         <v>14</v>
@@ -20081,7 +20076,7 @@
         <v>1</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="E408" s="1">
         <v>75</v>
@@ -20116,7 +20111,7 @@
     </row>
     <row r="409" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A409" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B409" s="1">
         <v>15</v>
@@ -20125,7 +20120,7 @@
         <v>1</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E409" s="1">
         <v>75</v>
@@ -20160,7 +20155,7 @@
     </row>
     <row r="410" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A410" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B410" s="1">
         <v>16</v>
@@ -20169,7 +20164,7 @@
         <v>1</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E410" s="1">
         <v>75</v>
@@ -20204,7 +20199,7 @@
     </row>
     <row r="411" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A411" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B411" s="1">
         <v>17</v>
@@ -20213,7 +20208,7 @@
         <v>1</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="E411" s="1">
         <v>75</v>
@@ -20248,7 +20243,7 @@
     </row>
     <row r="412" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A412" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B412" s="1">
         <v>18</v>
@@ -20257,7 +20252,7 @@
         <v>1</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E412" s="1">
         <v>75</v>
@@ -20292,7 +20287,7 @@
     </row>
     <row r="413" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A413" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B413" s="1">
         <v>19</v>
@@ -20301,7 +20296,7 @@
         <v>1</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E413" s="1">
         <v>75</v>
@@ -20336,7 +20331,7 @@
     </row>
     <row r="414" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A414" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B414" s="1">
         <v>20</v>
@@ -20345,7 +20340,7 @@
         <v>1</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="E414" s="1">
         <v>75</v>
@@ -20380,7 +20375,7 @@
     </row>
     <row r="415" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A415" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B415" s="1">
         <v>21</v>
@@ -20389,7 +20384,7 @@
         <v>1</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E415" s="1">
         <v>75</v>
@@ -20424,7 +20419,7 @@
     </row>
     <row r="416" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A416" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B416" s="1">
         <v>22</v>
@@ -20433,7 +20428,7 @@
         <v>1</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="E416" s="1">
         <v>75</v>
@@ -20468,7 +20463,7 @@
     </row>
     <row r="417" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A417" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B417" s="1">
         <v>23</v>
@@ -20477,7 +20472,7 @@
         <v>1</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E417" s="1">
         <v>75</v>
@@ -20512,7 +20507,7 @@
     </row>
     <row r="418" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A418" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B418" s="1">
         <v>24</v>
@@ -20521,7 +20516,7 @@
         <v>1</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E418" s="1">
         <v>75</v>
@@ -20556,7 +20551,7 @@
     </row>
     <row r="419" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A419" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B419" s="1">
         <v>25</v>
@@ -20565,7 +20560,7 @@
         <v>1</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="E419" s="1">
         <v>75</v>
@@ -20600,7 +20595,7 @@
     </row>
     <row r="420" spans="1:14" ht="114.75" x14ac:dyDescent="0.2">
       <c r="A420" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B420" s="1">
         <v>26</v>
@@ -20609,7 +20604,7 @@
         <v>1</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="E420" s="1">
         <v>75</v>
@@ -20644,7 +20639,7 @@
     </row>
     <row r="421" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A421" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B421" s="1">
         <v>27</v>
@@ -20653,7 +20648,7 @@
         <v>1</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E421" s="1">
         <v>75</v>
@@ -20688,7 +20683,7 @@
     </row>
     <row r="422" spans="1:14" ht="51" x14ac:dyDescent="0.2">
       <c r="A422" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B422" s="1">
         <v>28</v>
@@ -20697,7 +20692,7 @@
         <v>0</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="E422" s="1">
         <v>18</v>
@@ -20732,7 +20727,7 @@
     </row>
     <row r="423" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A423" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B423" s="1">
         <v>1</v>
@@ -20741,7 +20736,7 @@
         <v>1</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="E423" s="1">
         <v>75</v>
@@ -20776,7 +20771,7 @@
     </row>
     <row r="424" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A424" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B424" s="1">
         <v>2</v>
@@ -20785,7 +20780,7 @@
         <v>1</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E424" s="1">
         <v>75</v>
@@ -20820,7 +20815,7 @@
     </row>
     <row r="425" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A425" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B425" s="1">
         <v>3</v>
@@ -20829,7 +20824,7 @@
         <v>1</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="E425" s="1">
         <v>75</v>
@@ -20864,7 +20859,7 @@
     </row>
     <row r="426" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A426" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B426" s="1">
         <v>4</v>
@@ -20873,7 +20868,7 @@
         <v>1</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="E426" s="1">
         <v>75</v>
@@ -20908,7 +20903,7 @@
     </row>
     <row r="427" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A427" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B427" s="1">
         <v>5</v>
@@ -20917,7 +20912,7 @@
         <v>1</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="E427" s="1">
         <v>75</v>
@@ -20952,7 +20947,7 @@
     </row>
     <row r="428" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A428" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B428" s="1">
         <v>6</v>
@@ -20961,7 +20956,7 @@
         <v>1</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E428" s="1">
         <v>75</v>
@@ -20996,7 +20991,7 @@
     </row>
     <row r="429" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A429" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B429" s="1">
         <v>7</v>
@@ -21005,7 +21000,7 @@
         <v>1</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="E429" s="1">
         <v>75</v>
@@ -21040,7 +21035,7 @@
     </row>
     <row r="430" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A430" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B430" s="1">
         <v>8</v>
@@ -21049,7 +21044,7 @@
         <v>1</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E430" s="1">
         <v>75</v>
@@ -21084,7 +21079,7 @@
     </row>
     <row r="431" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A431" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B431" s="1">
         <v>9</v>
@@ -21093,7 +21088,7 @@
         <v>1</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E431" s="1">
         <v>75</v>
@@ -21128,7 +21123,7 @@
     </row>
     <row r="432" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A432" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B432" s="1">
         <v>10</v>
@@ -21137,7 +21132,7 @@
         <v>1</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="E432" s="1">
         <v>75</v>
@@ -21172,7 +21167,7 @@
     </row>
     <row r="433" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A433" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B433" s="1">
         <v>11</v>
@@ -21181,7 +21176,7 @@
         <v>1</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="E433" s="1">
         <v>75</v>
@@ -21216,7 +21211,7 @@
     </row>
     <row r="434" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A434" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B434" s="1">
         <v>12</v>
@@ -21225,7 +21220,7 @@
         <v>1</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E434" s="1">
         <v>75</v>
@@ -21260,7 +21255,7 @@
     </row>
     <row r="435" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A435" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B435" s="1">
         <v>13</v>
@@ -21269,7 +21264,7 @@
         <v>1</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="E435" s="1">
         <v>75</v>
@@ -21304,7 +21299,7 @@
     </row>
     <row r="436" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A436" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B436" s="1">
         <v>14</v>
@@ -21313,7 +21308,7 @@
         <v>1</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="E436" s="1">
         <v>75</v>
@@ -21348,7 +21343,7 @@
     </row>
     <row r="437" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A437" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B437" s="1">
         <v>15</v>
@@ -21357,7 +21352,7 @@
         <v>1</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E437" s="1">
         <v>75</v>
@@ -21392,7 +21387,7 @@
     </row>
     <row r="438" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A438" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B438" s="1">
         <v>16</v>
@@ -21401,7 +21396,7 @@
         <v>1</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="E438" s="1">
         <v>75</v>
@@ -21436,7 +21431,7 @@
     </row>
     <row r="439" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A439" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B439" s="1">
         <v>17</v>
@@ -21445,7 +21440,7 @@
         <v>1</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="E439" s="1">
         <v>75</v>
@@ -21480,7 +21475,7 @@
     </row>
     <row r="440" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A440" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B440" s="1">
         <v>18</v>
@@ -21489,7 +21484,7 @@
         <v>1</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E440" s="1">
         <v>75</v>
@@ -21524,7 +21519,7 @@
     </row>
     <row r="441" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A441" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B441" s="1">
         <v>19</v>
@@ -21533,7 +21528,7 @@
         <v>1</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="E441" s="1">
         <v>75</v>
@@ -21568,7 +21563,7 @@
     </row>
     <row r="442" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A442" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B442" s="1">
         <v>20</v>
@@ -21577,7 +21572,7 @@
         <v>1</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="E442" s="1">
         <v>75</v>
@@ -21612,7 +21607,7 @@
     </row>
     <row r="443" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A443" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B443" s="1">
         <v>21</v>
@@ -21621,7 +21616,7 @@
         <v>1</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E443" s="1">
         <v>75</v>
@@ -21656,7 +21651,7 @@
     </row>
     <row r="444" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A444" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B444" s="1">
         <v>22</v>
@@ -21665,7 +21660,7 @@
         <v>1</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="E444" s="1">
         <v>75</v>
@@ -21700,7 +21695,7 @@
     </row>
     <row r="445" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A445" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B445" s="1">
         <v>23</v>
@@ -21709,7 +21704,7 @@
         <v>1</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="E445" s="1">
         <v>75</v>
@@ -21744,7 +21739,7 @@
     </row>
     <row r="446" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A446" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B446" s="1">
         <v>24</v>
@@ -21753,7 +21748,7 @@
         <v>1</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E446" s="1">
         <v>75</v>
@@ -21788,7 +21783,7 @@
     </row>
     <row r="447" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A447" s="1" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B447" s="1">
         <v>25</v>
@@ -21797,7 +21792,7 @@
         <v>0</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="E447" s="1">
         <v>62</v>
@@ -21832,7 +21827,7 @@
     </row>
     <row r="448" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A448" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B448" s="1">
         <v>1</v>
@@ -21841,7 +21836,7 @@
         <v>1</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E448" s="1">
         <v>75</v>
@@ -21876,7 +21871,7 @@
     </row>
     <row r="449" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A449" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B449" s="1">
         <v>2</v>
@@ -21885,7 +21880,7 @@
         <v>1</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="E449" s="1">
         <v>75</v>
@@ -21920,7 +21915,7 @@
     </row>
     <row r="450" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A450" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B450" s="1">
         <v>3</v>
@@ -21929,7 +21924,7 @@
         <v>1</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="E450" s="1">
         <v>75</v>
@@ -21964,7 +21959,7 @@
     </row>
     <row r="451" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A451" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B451" s="1">
         <v>4</v>
@@ -21973,7 +21968,7 @@
         <v>1</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="E451" s="1">
         <v>75</v>
@@ -22008,7 +22003,7 @@
     </row>
     <row r="452" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A452" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B452" s="1">
         <v>5</v>
@@ -22017,7 +22012,7 @@
         <v>1</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="E452" s="1">
         <v>75</v>
@@ -22052,7 +22047,7 @@
     </row>
     <row r="453" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A453" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B453" s="1">
         <v>6</v>
@@ -22061,7 +22056,7 @@
         <v>1</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="E453" s="1">
         <v>75</v>
@@ -22096,7 +22091,7 @@
     </row>
     <row r="454" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A454" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B454" s="1">
         <v>7</v>
@@ -22105,7 +22100,7 @@
         <v>1</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E454" s="1">
         <v>75</v>
@@ -22140,7 +22135,7 @@
     </row>
     <row r="455" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A455" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B455" s="1">
         <v>8</v>
@@ -22149,7 +22144,7 @@
         <v>1</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="E455" s="1">
         <v>75</v>
@@ -22184,7 +22179,7 @@
     </row>
     <row r="456" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A456" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B456" s="1">
         <v>9</v>
@@ -22193,7 +22188,7 @@
         <v>1</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="E456" s="1">
         <v>75</v>
@@ -22228,7 +22223,7 @@
     </row>
     <row r="457" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A457" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B457" s="1">
         <v>10</v>
@@ -22237,7 +22232,7 @@
         <v>1</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E457" s="1">
         <v>75</v>
@@ -22272,7 +22267,7 @@
     </row>
     <row r="458" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A458" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B458" s="1">
         <v>11</v>
@@ -22281,7 +22276,7 @@
         <v>1</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="E458" s="1">
         <v>75</v>
@@ -22316,7 +22311,7 @@
     </row>
     <row r="459" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A459" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B459" s="1">
         <v>12</v>
@@ -22325,7 +22320,7 @@
         <v>1</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="E459" s="1">
         <v>75</v>
@@ -22360,7 +22355,7 @@
     </row>
     <row r="460" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A460" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B460" s="1">
         <v>13</v>
@@ -22369,7 +22364,7 @@
         <v>1</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E460" s="1">
         <v>75</v>
@@ -22404,7 +22399,7 @@
     </row>
     <row r="461" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A461" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B461" s="1">
         <v>14</v>
@@ -22413,7 +22408,7 @@
         <v>1</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="E461" s="1">
         <v>75</v>
@@ -22448,7 +22443,7 @@
     </row>
     <row r="462" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A462" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B462" s="1">
         <v>15</v>
@@ -22457,7 +22452,7 @@
         <v>1</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="E462" s="1">
         <v>75</v>
@@ -22492,7 +22487,7 @@
     </row>
     <row r="463" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A463" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B463" s="1">
         <v>16</v>
@@ -22501,7 +22496,7 @@
         <v>1</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E463" s="1">
         <v>75</v>
@@ -22536,7 +22531,7 @@
     </row>
     <row r="464" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A464" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B464" s="1">
         <v>17</v>
@@ -22545,7 +22540,7 @@
         <v>1</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="E464" s="1">
         <v>75</v>
@@ -22580,7 +22575,7 @@
     </row>
     <row r="465" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A465" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B465" s="1">
         <v>18</v>
@@ -22589,7 +22584,7 @@
         <v>1</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="E465" s="1">
         <v>75</v>
@@ -22624,7 +22619,7 @@
     </row>
     <row r="466" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A466" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B466" s="1">
         <v>19</v>
@@ -22633,7 +22628,7 @@
         <v>1</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E466" s="1">
         <v>75</v>
@@ -22668,7 +22663,7 @@
     </row>
     <row r="467" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A467" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B467" s="1">
         <v>20</v>
@@ -22677,7 +22672,7 @@
         <v>1</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="E467" s="1">
         <v>75</v>
@@ -22712,7 +22707,7 @@
     </row>
     <row r="468" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A468" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B468" s="1">
         <v>21</v>
@@ -22721,7 +22716,7 @@
         <v>1</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="E468" s="1">
         <v>75</v>
@@ -22756,7 +22751,7 @@
     </row>
     <row r="469" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A469" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B469" s="1">
         <v>22</v>
@@ -22765,7 +22760,7 @@
         <v>1</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E469" s="1">
         <v>75</v>
@@ -22800,7 +22795,7 @@
     </row>
     <row r="470" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A470" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B470" s="1">
         <v>23</v>
@@ -22809,7 +22804,7 @@
         <v>0</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="E470" s="1">
         <v>44</v>
@@ -22844,7 +22839,7 @@
     </row>
     <row r="471" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A471" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B471" s="1">
         <v>1</v>
@@ -22853,7 +22848,7 @@
         <v>1</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="E471" s="1">
         <v>75</v>
@@ -22888,7 +22883,7 @@
     </row>
     <row r="472" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A472" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B472" s="1">
         <v>2</v>
@@ -22897,7 +22892,7 @@
         <v>1</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E472" s="1">
         <v>75</v>
@@ -22932,7 +22927,7 @@
     </row>
     <row r="473" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A473" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B473" s="1">
         <v>3</v>
@@ -22941,7 +22936,7 @@
         <v>1</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="E473" s="1">
         <v>75</v>
@@ -22976,7 +22971,7 @@
     </row>
     <row r="474" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A474" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B474" s="1">
         <v>4</v>
@@ -22985,7 +22980,7 @@
         <v>1</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="E474" s="1">
         <v>75</v>
@@ -23020,7 +23015,7 @@
     </row>
     <row r="475" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A475" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B475" s="1">
         <v>5</v>
@@ -23029,7 +23024,7 @@
         <v>1</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E475" s="1">
         <v>75</v>
@@ -23064,7 +23059,7 @@
     </row>
     <row r="476" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A476" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B476" s="1">
         <v>6</v>
@@ -23073,7 +23068,7 @@
         <v>1</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="E476" s="1">
         <v>75</v>
@@ -23108,7 +23103,7 @@
     </row>
     <row r="477" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A477" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B477" s="1">
         <v>7</v>
@@ -23117,7 +23112,7 @@
         <v>1</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="E477" s="1">
         <v>75</v>
@@ -23152,7 +23147,7 @@
     </row>
     <row r="478" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A478" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B478" s="1">
         <v>8</v>
@@ -23161,7 +23156,7 @@
         <v>1</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E478" s="1">
         <v>75</v>
@@ -23196,7 +23191,7 @@
     </row>
     <row r="479" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A479" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B479" s="1">
         <v>9</v>
@@ -23205,7 +23200,7 @@
         <v>1</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="E479" s="1">
         <v>75</v>
@@ -23240,7 +23235,7 @@
     </row>
     <row r="480" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A480" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B480" s="1">
         <v>10</v>
@@ -23249,7 +23244,7 @@
         <v>1</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="E480" s="1">
         <v>75</v>
@@ -23284,7 +23279,7 @@
     </row>
     <row r="481" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A481" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B481" s="1">
         <v>11</v>
@@ -23293,7 +23288,7 @@
         <v>1</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E481" s="1">
         <v>75</v>
@@ -23328,7 +23323,7 @@
     </row>
     <row r="482" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A482" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B482" s="1">
         <v>12</v>
@@ -23337,7 +23332,7 @@
         <v>1</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="E482" s="1">
         <v>75</v>
@@ -23372,7 +23367,7 @@
     </row>
     <row r="483" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A483" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B483" s="1">
         <v>13</v>
@@ -23381,7 +23376,7 @@
         <v>1</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="E483" s="1">
         <v>75</v>
@@ -23416,7 +23411,7 @@
     </row>
     <row r="484" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A484" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B484" s="1">
         <v>14</v>
@@ -23425,7 +23420,7 @@
         <v>1</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E484" s="1">
         <v>75</v>
@@ -23460,7 +23455,7 @@
     </row>
     <row r="485" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A485" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B485" s="1">
         <v>15</v>
@@ -23469,7 +23464,7 @@
         <v>1</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="E485" s="1">
         <v>75</v>
@@ -23504,7 +23499,7 @@
     </row>
     <row r="486" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A486" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B486" s="1">
         <v>16</v>
@@ -23513,7 +23508,7 @@
         <v>1</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="E486" s="1">
         <v>75</v>
@@ -23548,7 +23543,7 @@
     </row>
     <row r="487" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A487" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B487" s="1">
         <v>17</v>
@@ -23557,7 +23552,7 @@
         <v>1</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E487" s="1">
         <v>75</v>
@@ -23592,7 +23587,7 @@
     </row>
     <row r="488" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A488" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B488" s="1">
         <v>18</v>
@@ -23601,7 +23596,7 @@
         <v>1</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E488" s="1">
         <v>75</v>
@@ -23636,7 +23631,7 @@
     </row>
     <row r="489" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A489" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B489" s="1">
         <v>19</v>
@@ -23645,7 +23640,7 @@
         <v>1</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E489" s="1">
         <v>75</v>
@@ -23680,7 +23675,7 @@
     </row>
     <row r="490" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A490" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B490" s="1">
         <v>20</v>
@@ -23689,7 +23684,7 @@
         <v>1</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E490" s="1">
         <v>75</v>
@@ -23724,7 +23719,7 @@
     </row>
     <row r="491" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A491" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B491" s="1">
         <v>21</v>
@@ -23733,7 +23728,7 @@
         <v>1</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E491" s="1">
         <v>75</v>
@@ -23768,7 +23763,7 @@
     </row>
     <row r="492" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A492" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B492" s="1">
         <v>22</v>
@@ -23777,7 +23772,7 @@
         <v>1</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="E492" s="1">
         <v>75</v>
@@ -23812,7 +23807,7 @@
     </row>
     <row r="493" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A493" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B493" s="1">
         <v>23</v>
@@ -23821,7 +23816,7 @@
         <v>1</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E493" s="1">
         <v>75</v>
@@ -23856,7 +23851,7 @@
     </row>
     <row r="494" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A494" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B494" s="1">
         <v>24</v>
@@ -23865,7 +23860,7 @@
         <v>1</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="E494" s="1">
         <v>75</v>
@@ -23900,7 +23895,7 @@
     </row>
     <row r="495" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A495" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B495" s="1">
         <v>25</v>
@@ -23909,7 +23904,7 @@
         <v>1</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="E495" s="1">
         <v>75</v>
@@ -23944,7 +23939,7 @@
     </row>
     <row r="496" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A496" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B496" s="1">
         <v>26</v>
@@ -23953,7 +23948,7 @@
         <v>1</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E496" s="1">
         <v>75</v>
@@ -23988,7 +23983,7 @@
     </row>
     <row r="497" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A497" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B497" s="1">
         <v>27</v>
@@ -23997,7 +23992,7 @@
         <v>1</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E497" s="1">
         <v>75</v>
@@ -24032,7 +24027,7 @@
     </row>
     <row r="498" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A498" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B498" s="1">
         <v>28</v>
@@ -24041,7 +24036,7 @@
         <v>1</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="E498" s="1">
         <v>75</v>
@@ -24076,7 +24071,7 @@
     </row>
     <row r="499" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A499" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B499" s="1">
         <v>29</v>
@@ -24085,7 +24080,7 @@
         <v>1</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E499" s="1">
         <v>75</v>
@@ -24120,7 +24115,7 @@
     </row>
     <row r="500" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A500" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B500" s="1">
         <v>30</v>
@@ -24129,7 +24124,7 @@
         <v>1</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="E500" s="1">
         <v>75</v>
@@ -24164,7 +24159,7 @@
     </row>
     <row r="501" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A501" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B501" s="1">
         <v>31</v>
@@ -24173,7 +24168,7 @@
         <v>1</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="E501" s="1">
         <v>75</v>
@@ -24208,7 +24203,7 @@
     </row>
     <row r="502" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A502" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B502" s="1">
         <v>32</v>
@@ -24217,7 +24212,7 @@
         <v>1</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E502" s="1">
         <v>75</v>
@@ -24252,7 +24247,7 @@
     </row>
     <row r="503" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A503" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B503" s="1">
         <v>33</v>
@@ -24261,7 +24256,7 @@
         <v>1</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E503" s="1">
         <v>75</v>
@@ -24296,7 +24291,7 @@
     </row>
     <row r="504" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A504" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B504" s="1">
         <v>34</v>
@@ -24305,7 +24300,7 @@
         <v>1</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="E504" s="1">
         <v>75</v>
@@ -24340,7 +24335,7 @@
     </row>
     <row r="505" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A505" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B505" s="1">
         <v>35</v>
@@ -24349,7 +24344,7 @@
         <v>1</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E505" s="1">
         <v>75</v>
@@ -24384,7 +24379,7 @@
     </row>
     <row r="506" spans="1:14" ht="76.5" x14ac:dyDescent="0.2">
       <c r="A506" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B506" s="1">
         <v>36</v>
@@ -24393,7 +24388,7 @@
         <v>1</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E506" s="1">
         <v>75</v>
@@ -24428,7 +24423,7 @@
     </row>
     <row r="507" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A507" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B507" s="1">
         <v>37</v>
@@ -24437,7 +24432,7 @@
         <v>1</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="E507" s="1">
         <v>75</v>
@@ -24472,7 +24467,7 @@
     </row>
     <row r="508" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A508" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B508" s="1">
         <v>38</v>
@@ -24481,7 +24476,7 @@
         <v>1</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E508" s="1">
         <v>75</v>
@@ -24516,7 +24511,7 @@
     </row>
     <row r="509" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A509" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B509" s="1">
         <v>39</v>
@@ -24525,7 +24520,7 @@
         <v>1</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="E509" s="1">
         <v>75</v>
@@ -24560,7 +24555,7 @@
     </row>
     <row r="510" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A510" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B510" s="1">
         <v>40</v>
@@ -24569,7 +24564,7 @@
         <v>1</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="E510" s="1">
         <v>75</v>
@@ -24604,7 +24599,7 @@
     </row>
     <row r="511" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A511" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B511" s="1">
         <v>41</v>
@@ -24613,7 +24608,7 @@
         <v>1</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E511" s="1">
         <v>75</v>
@@ -24648,7 +24643,7 @@
     </row>
     <row r="512" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A512" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B512" s="1">
         <v>42</v>
@@ -24657,7 +24652,7 @@
         <v>1</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E512" s="1">
         <v>75</v>
@@ -24692,7 +24687,7 @@
     </row>
     <row r="513" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A513" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B513" s="1">
         <v>43</v>
@@ -24701,7 +24696,7 @@
         <v>1</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="E513" s="1">
         <v>75</v>
@@ -24736,7 +24731,7 @@
     </row>
     <row r="514" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A514" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B514" s="1">
         <v>44</v>
@@ -24745,7 +24740,7 @@
         <v>1</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="E514" s="1">
         <v>75</v>
@@ -24780,7 +24775,7 @@
     </row>
     <row r="515" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A515" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B515" s="1">
         <v>45</v>
@@ -24789,7 +24784,7 @@
         <v>1</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E515" s="1">
         <v>75</v>
@@ -24824,7 +24819,7 @@
     </row>
     <row r="516" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A516" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B516" s="1">
         <v>46</v>
@@ -24833,7 +24828,7 @@
         <v>1</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="E516" s="1">
         <v>75</v>
@@ -24868,7 +24863,7 @@
     </row>
     <row r="517" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A517" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B517" s="1">
         <v>47</v>
@@ -24877,7 +24872,7 @@
         <v>1</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="E517" s="1">
         <v>75</v>
@@ -24912,7 +24907,7 @@
     </row>
     <row r="518" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A518" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B518" s="1">
         <v>48</v>
@@ -24921,7 +24916,7 @@
         <v>1</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E518" s="1">
         <v>75</v>
@@ -24956,7 +24951,7 @@
     </row>
     <row r="519" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A519" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B519" s="1">
         <v>49</v>
@@ -24965,7 +24960,7 @@
         <v>1</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E519" s="1">
         <v>75</v>
@@ -25000,7 +24995,7 @@
     </row>
     <row r="520" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A520" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B520" s="1">
         <v>50</v>
@@ -25009,7 +25004,7 @@
         <v>1</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="E520" s="1">
         <v>75</v>
@@ -25044,7 +25039,7 @@
     </row>
     <row r="521" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A521" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B521" s="1">
         <v>51</v>
@@ -25053,7 +25048,7 @@
         <v>1</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="E521" s="1">
         <v>75</v>
@@ -25088,7 +25083,7 @@
     </row>
     <row r="522" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A522" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B522" s="1">
         <v>52</v>
@@ -25097,7 +25092,7 @@
         <v>1</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E522" s="1">
         <v>75</v>
@@ -25132,7 +25127,7 @@
     </row>
     <row r="523" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A523" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B523" s="1">
         <v>53</v>
@@ -25141,7 +25136,7 @@
         <v>1</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="E523" s="1">
         <v>75</v>
@@ -25176,7 +25171,7 @@
     </row>
     <row r="524" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A524" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B524" s="1">
         <v>54</v>
@@ -25185,7 +25180,7 @@
         <v>1</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E524" s="1">
         <v>75</v>
@@ -25220,7 +25215,7 @@
     </row>
     <row r="525" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A525" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B525" s="1">
         <v>55</v>
@@ -25229,7 +25224,7 @@
         <v>1</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="E525" s="1">
         <v>75</v>
@@ -25264,7 +25259,7 @@
     </row>
     <row r="526" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A526" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B526" s="1">
         <v>56</v>
@@ -25273,7 +25268,7 @@
         <v>1</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="E526" s="1">
         <v>75</v>
@@ -25308,7 +25303,7 @@
     </row>
     <row r="527" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A527" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B527" s="1">
         <v>57</v>
@@ -25317,7 +25312,7 @@
         <v>1</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="E527" s="1">
         <v>75</v>
@@ -25352,7 +25347,7 @@
     </row>
     <row r="528" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A528" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B528" s="1">
         <v>58</v>
@@ -25361,7 +25356,7 @@
         <v>0</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E528" s="1">
         <v>19</v>
@@ -25396,7 +25391,7 @@
     </row>
     <row r="529" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A529" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B529" s="1">
         <v>1</v>
@@ -25405,7 +25400,7 @@
         <v>1</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="E529" s="1">
         <v>75</v>
@@ -25440,7 +25435,7 @@
     </row>
     <row r="530" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A530" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B530" s="1">
         <v>2</v>
@@ -25449,7 +25444,7 @@
         <v>1</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="E530" s="1">
         <v>75</v>
@@ -25484,7 +25479,7 @@
     </row>
     <row r="531" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A531" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B531" s="1">
         <v>3</v>
@@ -25493,7 +25488,7 @@
         <v>1</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="E531" s="1">
         <v>75</v>
@@ -25528,7 +25523,7 @@
     </row>
     <row r="532" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A532" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B532" s="1">
         <v>4</v>
@@ -25537,7 +25532,7 @@
         <v>1</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E532" s="1">
         <v>75</v>
@@ -25572,7 +25567,7 @@
     </row>
     <row r="533" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A533" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B533" s="1">
         <v>5</v>
@@ -25581,7 +25576,7 @@
         <v>1</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="E533" s="1">
         <v>75</v>
@@ -25616,7 +25611,7 @@
     </row>
     <row r="534" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A534" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B534" s="1">
         <v>6</v>
@@ -25625,7 +25620,7 @@
         <v>1</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="E534" s="1">
         <v>75</v>
@@ -25660,7 +25655,7 @@
     </row>
     <row r="535" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A535" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B535" s="1">
         <v>7</v>
@@ -25669,7 +25664,7 @@
         <v>1</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E535" s="1">
         <v>75</v>
@@ -25704,7 +25699,7 @@
     </row>
     <row r="536" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A536" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B536" s="1">
         <v>8</v>
@@ -25713,7 +25708,7 @@
         <v>1</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="E536" s="1">
         <v>75</v>
@@ -25748,7 +25743,7 @@
     </row>
     <row r="537" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A537" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B537" s="1">
         <v>9</v>
@@ -25757,7 +25752,7 @@
         <v>1</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="E537" s="1">
         <v>75</v>
@@ -25792,7 +25787,7 @@
     </row>
     <row r="538" spans="1:14" ht="89.25" x14ac:dyDescent="0.2">
       <c r="A538" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B538" s="1">
         <v>10</v>
@@ -25801,7 +25796,7 @@
         <v>1</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E538" s="1">
         <v>75</v>
@@ -25836,7 +25831,7 @@
     </row>
     <row r="539" spans="1:14" ht="63.75" x14ac:dyDescent="0.2">
       <c r="A539" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B539" s="1">
         <v>11</v>
@@ -25845,7 +25840,7 @@
         <v>0</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="E539" s="1">
         <v>58</v>
@@ -25999,7 +25994,7 @@
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B2">
         <v>15</v>
@@ -26076,7 +26071,7 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B3">
         <v>11</v>
@@ -26153,7 +26148,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4">
         <v>8</v>
@@ -26230,7 +26225,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5">
         <v>3</v>
@@ -26307,7 +26302,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6">
         <v>8</v>
@@ -26384,7 +26379,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B7">
         <v>49</v>
@@ -26461,7 +26456,7 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B8">
         <v>61</v>
@@ -26538,7 +26533,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="B9">
         <v>60</v>
@@ -26615,7 +26610,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B10">
         <v>83</v>
@@ -26692,7 +26687,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B11">
         <v>20</v>
@@ -26769,7 +26764,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B12">
         <v>64</v>
@@ -26846,7 +26841,7 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B13">
         <v>27</v>
@@ -26923,7 +26918,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B14">
         <v>24</v>
@@ -27000,7 +26995,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B15">
         <v>22</v>
@@ -27077,7 +27072,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B16">
         <v>57</v>
@@ -27154,7 +27149,7 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B17">
         <v>10</v>
